--- a/data-raw/NT/Revenue.xlsx
+++ b/data-raw/NT/Revenue.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\4983\Documents\tax4sa\data-raw\NT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F41ED33-A1A3-438A-8879-3AB94A7E1532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93CD9837-A849-418E-90D2-4E0FA947A32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Annual" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="447">
   <si>
     <t>April_2006</t>
   </si>
@@ -1325,6 +1325,57 @@
   <si>
     <t>2024/25</t>
   </si>
+  <si>
+    <t>May_2025</t>
+  </si>
+  <si>
+    <t>June_2025</t>
+  </si>
+  <si>
+    <t>July_2025</t>
+  </si>
+  <si>
+    <t>August_2025</t>
+  </si>
+  <si>
+    <t>September_2025</t>
+  </si>
+  <si>
+    <t>October_2025</t>
+  </si>
+  <si>
+    <t>November_2025</t>
+  </si>
+  <si>
+    <t>December_2025</t>
+  </si>
+  <si>
+    <t>January_2026</t>
+  </si>
+  <si>
+    <t>February_2026</t>
+  </si>
+  <si>
+    <t>March_2026</t>
+  </si>
+  <si>
+    <t>April_2026</t>
+  </si>
+  <si>
+    <t>May_2026</t>
+  </si>
+  <si>
+    <t>June_2026</t>
+  </si>
+  <si>
+    <t>July_2026</t>
+  </si>
+  <si>
+    <t>August_2026</t>
+  </si>
+  <si>
+    <t>2025/26</t>
+  </si>
 </sst>
 </file>
 
@@ -1641,11 +1692,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AS76"/>
+  <dimension ref="A1:AT76"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.453125" customWidth="1"/>
-    <col min="2" max="2" width="30.90625" customWidth="1"/>
+    <col min="1" max="1" width="3.26953125" customWidth="1"/>
+    <col min="2" max="2" width="5.26953125" customWidth="1"/>
     <col min="3" max="3" width="29.6328125" customWidth="1"/>
     <col min="4" max="9" width="12.453125" customWidth="1"/>
     <col min="10" max="14" width="13.08984375" customWidth="1"/>
@@ -1657,9 +1708,10 @@
     <col min="43" max="43" width="12.90625" customWidth="1"/>
     <col min="44" max="44" width="15.7265625" customWidth="1"/>
     <col min="45" max="45" width="12.36328125" customWidth="1"/>
+    <col min="46" max="46" width="14.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>242</v>
       </c>
@@ -1795,8 +1847,11 @@
       <c r="AS1" t="s">
         <v>429</v>
       </c>
+      <c r="AT1" t="s">
+        <v>446</v>
+      </c>
     </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>247</v>
       </c>
@@ -1943,8 +1998,12 @@
         <f>SUM(Monthly!JH2:JS2)</f>
         <v>1100529906.5327702</v>
       </c>
+      <c r="AT2">
+        <f>SUM(Monthly!JT2:KE2)</f>
+        <v>1190241487.5227101</v>
+      </c>
     </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>247</v>
       </c>
@@ -2082,8 +2141,12 @@
         <f>SUM(Monthly!JH3:JS3)</f>
         <v>729910987.28751004</v>
       </c>
+      <c r="AT3">
+        <f>SUM(Monthly!JT3:KE3)</f>
+        <v>790619211.14304996</v>
+      </c>
     </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>247</v>
       </c>
@@ -2225,8 +2288,12 @@
         <f>SUM(Monthly!JH9:JS9)</f>
         <v>362871331.8867799</v>
       </c>
+      <c r="AT4">
+        <f>SUM(Monthly!JT9:KE9)</f>
+        <v>392380425.24212009</v>
+      </c>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>247</v>
       </c>
@@ -2364,8 +2431,12 @@
         <f>SUM(Monthly!JH10:JS10)</f>
         <v>318739343.86049002</v>
       </c>
+      <c r="AT5">
+        <f>SUM(Monthly!JT10:KE10)</f>
+        <v>345432053.87557006</v>
+      </c>
     </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>247</v>
       </c>
@@ -2473,8 +2544,12 @@
         <f>SUM(Monthly!JH11:JS11)</f>
         <v>14841.0653</v>
       </c>
+      <c r="AT6">
+        <f>SUM(Monthly!JT11:KE11)</f>
+        <v>7982.8981800000001</v>
+      </c>
     </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>247</v>
       </c>
@@ -2492,8 +2567,12 @@
         <f>SUM(Monthly!JH12:JS12)</f>
         <v>42973231.255430005</v>
       </c>
+      <c r="AT7">
+        <f>SUM(Monthly!JT12:KE12)</f>
+        <v>45876461.714030005</v>
+      </c>
     </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>247</v>
       </c>
@@ -2544,8 +2623,12 @@
         <f>SUM(Monthly!JH13:JS13)</f>
         <v>1143915.7055600001</v>
       </c>
+      <c r="AT8">
+        <f>SUM(Monthly!JT13:KE13)</f>
+        <v>1063926.75434</v>
+      </c>
     </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>247</v>
       </c>
@@ -2604,7 +2687,7 @@
         <v>188647</v>
       </c>
     </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>247</v>
       </c>
@@ -2663,7 +2746,7 @@
         <v>320437</v>
       </c>
     </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>247</v>
       </c>
@@ -2722,7 +2805,7 @@
         <v>1677585</v>
       </c>
     </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>247</v>
       </c>
@@ -2784,7 +2867,7 @@
         <v>159.43700000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>247</v>
       </c>
@@ -2840,7 +2923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>247</v>
       </c>
@@ -2861,8 +2944,12 @@
         <f>SUM(Monthly!JH15:JS15)</f>
         <v>10976598.82299</v>
       </c>
+      <c r="AT14">
+        <f>SUM(Monthly!JT15:KE15)</f>
+        <v>10079174.45768</v>
+      </c>
     </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>247</v>
       </c>
@@ -2927,7 +3014,7 @@
         <v>-24</v>
       </c>
     </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>247</v>
       </c>
@@ -2986,7 +3073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>247</v>
       </c>
@@ -3124,8 +3211,12 @@
         <f>SUM(Monthly!JH16:JS16)</f>
         <v>7747587.3584799999</v>
       </c>
+      <c r="AT17">
+        <f>SUM(Monthly!JT16:KE16)</f>
+        <v>7241850.1476600002</v>
+      </c>
     </row>
-    <row r="18" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>247</v>
       </c>
@@ -3197,8 +3288,12 @@
         <f>SUM(Monthly!JH17:JS17)</f>
         <v>0</v>
       </c>
+      <c r="AT18">
+        <f>SUM(Monthly!JT17:KE17)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>192</v>
       </c>
@@ -3288,8 +3383,12 @@
         <f>SUM(Monthly!JH18:JS18)</f>
         <v>24447989.139509998</v>
       </c>
+      <c r="AT19">
+        <f>SUM(Monthly!JT18:KE18)</f>
+        <v>25977692.358840004</v>
+      </c>
     </row>
-    <row r="20" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>192</v>
       </c>
@@ -3379,8 +3478,12 @@
         <f>SUM(Monthly!JH19:JS19)</f>
         <v>24447989.139509998</v>
       </c>
+      <c r="AT20">
+        <f>SUM(Monthly!JT19:KE19)</f>
+        <v>25977692.358840004</v>
+      </c>
     </row>
-    <row r="21" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>194</v>
       </c>
@@ -3527,8 +3630,12 @@
         <f>SUM(Monthly!JH20:JS20)</f>
         <v>22505089.280309997</v>
       </c>
+      <c r="AT21">
+        <f>SUM(Monthly!JT20:KE20)</f>
+        <v>26345072.808630001</v>
+      </c>
     </row>
-    <row r="22" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>194</v>
       </c>
@@ -3666,8 +3773,12 @@
         <f>SUM(Monthly!JH22:JS22)</f>
         <v>1144497.6605799999</v>
       </c>
+      <c r="AT22">
+        <f>SUM(Monthly!JT22:KE22)</f>
+        <v>1368519.8536</v>
+      </c>
     </row>
-    <row r="23" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>194</v>
       </c>
@@ -3805,8 +3916,12 @@
         <f>SUM(Monthly!JH23:JS23)</f>
         <v>4035860.7750699995</v>
       </c>
+      <c r="AT23">
+        <f>SUM(Monthly!JT23:KE23)</f>
+        <v>4634544.87194</v>
+      </c>
     </row>
-    <row r="24" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>194</v>
       </c>
@@ -3944,8 +4059,12 @@
         <f>SUM(Monthly!JH25:JS25)</f>
         <v>5958032.2576599997</v>
       </c>
+      <c r="AT24">
+        <f>SUM(Monthly!JT25:KE25)</f>
+        <v>7551538.9238799997</v>
+      </c>
     </row>
-    <row r="25" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>194</v>
       </c>
@@ -4083,8 +4202,12 @@
         <f>SUM(Monthly!JH26:JS26)</f>
         <v>11366698.587000001</v>
       </c>
+      <c r="AT25">
+        <f>SUM(Monthly!JT26:KE26)</f>
+        <v>12790469.159210002</v>
+      </c>
     </row>
-    <row r="26" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>194</v>
       </c>
@@ -4107,7 +4230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>293</v>
       </c>
@@ -4254,8 +4377,12 @@
         <f>SUM(Monthly!JH27:JS27)</f>
         <v>627973090.92920995</v>
       </c>
+      <c r="AT27">
+        <f>SUM(Monthly!JT27:KE27)</f>
+        <v>683567011.07602</v>
+      </c>
     </row>
-    <row r="28" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>293</v>
       </c>
@@ -4405,8 +4532,12 @@
         <f>SUM(Monthly!JH28:JS28)</f>
         <v>457788790.28143007</v>
       </c>
+      <c r="AT28">
+        <f>SUM(Monthly!JT28:KE28)</f>
+        <v>500586607.18181002</v>
+      </c>
     </row>
-    <row r="29" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>293</v>
       </c>
@@ -4466,8 +4597,12 @@
         <f>SUM(Monthly!JH29:JS29)</f>
         <v>561407293.62182999</v>
       </c>
+      <c r="AT29">
+        <f>SUM(Monthly!JT29:KE29)</f>
+        <v>603957914.19336998</v>
+      </c>
     </row>
-    <row r="30" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>293</v>
       </c>
@@ -4527,8 +4662,12 @@
         <f>SUM(Monthly!JH30:JS30)</f>
         <v>261878360.66328996</v>
       </c>
+      <c r="AT30">
+        <f>SUM(Monthly!JT30:KE30)</f>
+        <v>267727294.76297003</v>
+      </c>
     </row>
-    <row r="31" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>293</v>
       </c>
@@ -4588,8 +4727,12 @@
         <f>SUM(Monthly!JH31:JS31)</f>
         <v>-365496864.00369</v>
       </c>
+      <c r="AT31">
+        <f>SUM(Monthly!JT31:KE31)</f>
+        <v>-371098601.77452999</v>
+      </c>
     </row>
-    <row r="32" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>293</v>
       </c>
@@ -4600,7 +4743,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="33" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>293</v>
       </c>
@@ -4738,8 +4881,12 @@
         <f>SUM(Monthly!JH34:JS34)</f>
         <v>24950479.342069998</v>
       </c>
+      <c r="AT33">
+        <f>SUM(Monthly!JT34:KE34)</f>
+        <v>27429319.841329999</v>
+      </c>
     </row>
-    <row r="34" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>293</v>
       </c>
@@ -4853,8 +5000,12 @@
         <f>SUM(Monthly!JH35:JS35)</f>
         <v>7744.8674499999997</v>
       </c>
+      <c r="AT34">
+        <f>SUM(Monthly!JT35:KE35)</f>
+        <v>3665.9107800000002</v>
+      </c>
     </row>
-    <row r="35" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>293</v>
       </c>
@@ -4992,8 +5143,12 @@
         <f>SUM(Monthly!JH36:JS36)</f>
         <v>7640938.3053799998</v>
       </c>
+      <c r="AT35">
+        <f>SUM(Monthly!JT36:KE36)</f>
+        <v>7690413.12708</v>
+      </c>
     </row>
-    <row r="36" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>293</v>
       </c>
@@ -5074,8 +5229,12 @@
         <f>SUM(Monthly!JH37:JS37)</f>
         <v>0</v>
       </c>
+      <c r="AT36">
+        <f>SUM(Monthly!JT37:KE37)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="37" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>293</v>
       </c>
@@ -5213,8 +5372,12 @@
         <f>SUM(Monthly!JH38:JS38)</f>
         <v>14450483.528890001</v>
       </c>
+      <c r="AT37">
+        <f>SUM(Monthly!JT38:KE38)</f>
+        <v>14403849.275749998</v>
+      </c>
     </row>
-    <row r="38" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>293</v>
       </c>
@@ -5352,8 +5515,12 @@
         <f>SUM(Monthly!JH39:JS39)</f>
         <v>9000465.7547399998</v>
       </c>
+      <c r="AT38">
+        <f>SUM(Monthly!JT39:KE39)</f>
+        <v>8612378.6173999999</v>
+      </c>
     </row>
-    <row r="39" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>293</v>
       </c>
@@ -5491,8 +5658,12 @@
         <f>SUM(Monthly!JH42:JS42)</f>
         <v>423576.91621000005</v>
       </c>
+      <c r="AT39">
+        <f>SUM(Monthly!JT42:KE42)</f>
+        <v>504910.82677999994</v>
+      </c>
     </row>
-    <row r="40" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>293</v>
       </c>
@@ -5630,8 +5801,12 @@
         <f>SUM(Monthly!JH43:JS43)</f>
         <v>679810.86226999981</v>
       </c>
+      <c r="AT40">
+        <f>SUM(Monthly!JT43:KE43)</f>
+        <v>452636.10305000003</v>
+      </c>
     </row>
-    <row r="41" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>293</v>
       </c>
@@ -5696,7 +5871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>293</v>
       </c>
@@ -5737,7 +5912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>293</v>
       </c>
@@ -5875,8 +6050,12 @@
         <f>SUM(Monthly!JH44:JS44)</f>
         <v>2523621.5609599999</v>
       </c>
+      <c r="AT43">
+        <f>SUM(Monthly!JT44:KE44)</f>
+        <v>2638262.1315299999</v>
+      </c>
     </row>
-    <row r="44" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>293</v>
       </c>
@@ -5921,8 +6100,12 @@
         <f>SUM(Monthly!JH46:JS46)</f>
         <v>2282234.2151500001</v>
       </c>
+      <c r="AT44">
+        <f>SUM(Monthly!JT46:KE46)</f>
+        <v>2347072.8210499999</v>
+      </c>
     </row>
-    <row r="45" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>293</v>
       </c>
@@ -6060,8 +6243,12 @@
         <f>SUM(Monthly!JH45:JS45)</f>
         <v>6969758.3562799999</v>
       </c>
+      <c r="AT45">
+        <f>SUM(Monthly!JT45:KE45)</f>
+        <v>7998435.5914200004</v>
+      </c>
     </row>
-    <row r="46" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>293</v>
       </c>
@@ -6187,8 +6374,12 @@
         <f>SUM(Monthly!JH47:JS47)</f>
         <v>85882626.668000013</v>
       </c>
+      <c r="AT46">
+        <f>SUM(Monthly!JT47:KE47)</f>
+        <v>95205717.319650009</v>
+      </c>
     </row>
-    <row r="47" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>293</v>
       </c>
@@ -6280,7 +6471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>293</v>
       </c>
@@ -6370,8 +6561,12 @@
         <f>SUM(Monthly!JH53:JS53)</f>
         <v>1021318.2980599999</v>
       </c>
+      <c r="AT48">
+        <f>SUM(Monthly!JT53:KE53)</f>
+        <v>1097180.4089299999</v>
+      </c>
     </row>
-    <row r="49" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>293</v>
       </c>
@@ -6436,7 +6631,7 @@
         <v>-4495</v>
       </c>
     </row>
-    <row r="50" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>293</v>
       </c>
@@ -6520,8 +6715,12 @@
         <f>SUM(Monthly!JH54:JS54)</f>
         <v>698712.48433000012</v>
       </c>
+      <c r="AT50">
+        <f>SUM(Monthly!JT54:KE54)</f>
+        <v>634702.40298000001</v>
+      </c>
     </row>
-    <row r="51" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>293</v>
       </c>
@@ -6596,8 +6795,12 @@
         <f>SUM(Monthly!JH55:JS55)</f>
         <v>7536175.130619999</v>
       </c>
+      <c r="AT51">
+        <f>SUM(Monthly!JT55:KE55)</f>
+        <v>7171538.1895599999</v>
+      </c>
     </row>
-    <row r="52" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>293</v>
       </c>
@@ -6663,8 +6866,12 @@
         <f>SUM(Monthly!JH56:JS56)</f>
         <v>9834.5069499999991</v>
       </c>
+      <c r="AT52">
+        <f>SUM(Monthly!JT56:KE56)</f>
+        <v>8195.1487699999998</v>
+      </c>
     </row>
-    <row r="53" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>293</v>
       </c>
@@ -6730,8 +6937,12 @@
         <f>SUM(Monthly!JH57:JS57)</f>
         <v>3045104.75294</v>
       </c>
+      <c r="AT53">
+        <f>SUM(Monthly!JT57:KE57)</f>
+        <v>3780233.32803</v>
+      </c>
     </row>
-    <row r="54" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>293</v>
       </c>
@@ -6779,8 +6990,12 @@
         <f>SUM(Monthly!JH58:JS58)</f>
         <v>773705.9728600001</v>
       </c>
+      <c r="AT54">
+        <f>SUM(Monthly!JT58:KE58)</f>
+        <v>792178.35675000004</v>
+      </c>
     </row>
-    <row r="55" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>293</v>
       </c>
@@ -6825,8 +7040,12 @@
         <f>SUM(Monthly!JH59:JS59)</f>
         <v>7556.6449099999991</v>
       </c>
+      <c r="AT55">
+        <f>SUM(Monthly!JT59:KE59)</f>
+        <v>7826.8113000000003</v>
+      </c>
     </row>
-    <row r="56" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>293</v>
       </c>
@@ -6892,8 +7111,12 @@
         <f>SUM(Monthly!JH60:JS60)</f>
         <v>2024313.0226299998</v>
       </c>
+      <c r="AT56">
+        <f>SUM(Monthly!JT60:KE60)</f>
+        <v>1911844.9689100003</v>
+      </c>
     </row>
-    <row r="57" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>293</v>
       </c>
@@ -6920,8 +7143,12 @@
         <f>SUM(Monthly!JH32:JS32)</f>
         <v>0</v>
       </c>
+      <c r="AT57">
+        <f>SUM(Monthly!JT32:KE32)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>293</v>
       </c>
@@ -6944,7 +7171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>293</v>
       </c>
@@ -6967,7 +7194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>293</v>
       </c>
@@ -7038,7 +7265,7 @@
         <v>270339</v>
       </c>
     </row>
-    <row r="61" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>293</v>
       </c>
@@ -7055,7 +7282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>293</v>
       </c>
@@ -7145,8 +7372,12 @@
         <f>SUM(Monthly!JH64:JS64)</f>
         <v>241868.06606999997</v>
       </c>
+      <c r="AT62">
+        <f>SUM(Monthly!JT64:KE64)</f>
+        <v>275541.96539999999</v>
+      </c>
     </row>
-    <row r="63" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>229</v>
       </c>
@@ -7293,8 +7524,12 @@
         <f>SUM(Monthly!JH65:JS65)</f>
         <v>79825692.96935001</v>
       </c>
+      <c r="AT63">
+        <f>SUM(Monthly!JT65:KE65)</f>
+        <v>84259987.61108999</v>
+      </c>
     </row>
-    <row r="64" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>229</v>
       </c>
@@ -7432,8 +7667,12 @@
         <f>SUM(Monthly!JH67:JS67)</f>
         <v>67338351.456549987</v>
       </c>
+      <c r="AT64">
+        <f>SUM(Monthly!JT67:KE67)</f>
+        <v>71990993.701460004</v>
+      </c>
     </row>
-    <row r="65" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>229</v>
       </c>
@@ -7507,7 +7746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>229</v>
       </c>
@@ -7552,8 +7791,12 @@
         <f>SUM(Monthly!JH71:JS71)</f>
         <v>140431.25998</v>
       </c>
+      <c r="AT66">
+        <f>SUM(Monthly!JT71:KE71)</f>
+        <v>162825.98607000001</v>
+      </c>
     </row>
-    <row r="67" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>229</v>
       </c>
@@ -7606,7 +7849,7 @@
         <v>5130</v>
       </c>
     </row>
-    <row r="68" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>229</v>
       </c>
@@ -7744,8 +7987,12 @@
         <f>SUM(Monthly!JH73:JS73)</f>
         <v>2454588.5237299995</v>
       </c>
+      <c r="AT68">
+        <f>SUM(Monthly!JT73:KE73)</f>
+        <v>2188121.4900199999</v>
+      </c>
     </row>
-    <row r="69" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>229</v>
       </c>
@@ -7865,8 +8112,12 @@
         <f>SUM(Monthly!JH74:JS74)</f>
         <v>65312.047450000005</v>
       </c>
+      <c r="AT69">
+        <f>SUM(Monthly!JT74:KE74)</f>
+        <v>63409.874719999993</v>
+      </c>
     </row>
-    <row r="70" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>229</v>
       </c>
@@ -7890,8 +8141,12 @@
         <f>SUM(Monthly!JH75:JS75)</f>
         <v>467242.82726000011</v>
       </c>
+      <c r="AT70">
+        <f>SUM(Monthly!JT75:KE75)</f>
+        <v>310250.97988</v>
+      </c>
     </row>
-    <row r="71" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>236</v>
       </c>
@@ -8038,8 +8293,12 @@
         <f>SUM(Monthly!JH76:JS76)</f>
         <v>0</v>
       </c>
+      <c r="AT71">
+        <f>SUM(Monthly!JT76:KE76)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>236</v>
       </c>
@@ -8177,8 +8436,12 @@
         <f>SUM(Monthly!JH77:JS77)</f>
         <v>0</v>
       </c>
+      <c r="AT72">
+        <f>SUM(Monthly!JT77:KE77)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>238</v>
       </c>
@@ -8274,8 +8537,12 @@
         <f>SUM(Monthly!JH78:JS78)</f>
         <v>-11635.93965</v>
       </c>
+      <c r="AT73">
+        <f>SUM(Monthly!JT78:KE78)</f>
+        <v>-50845.852189999998</v>
+      </c>
     </row>
-    <row r="74" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>239</v>
       </c>
@@ -8413,8 +8680,12 @@
         <f>SUM(Monthly!JH79:JS79)</f>
         <v>1855270132.9115</v>
       </c>
+      <c r="AT74">
+        <f>SUM(Monthly!JT79:KE79)</f>
+        <v>2010340404.3059099</v>
+      </c>
     </row>
-    <row r="75" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>240</v>
       </c>
@@ -8552,8 +8823,12 @@
         <f>SUM(Monthly!JH80:JS80)</f>
         <v>-89874116</v>
       </c>
+      <c r="AT75">
+        <f>SUM(Monthly!JT80:KE80)</f>
+        <v>-73552115</v>
+      </c>
     </row>
-    <row r="76" spans="1:45" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:46" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>241</v>
       </c>
@@ -8690,20 +8965,21 @@
       <c r="AS76">
         <f>SUM(Monthly!JH81:JS81)</f>
         <v>1765396016.9115</v>
+      </c>
+      <c r="AT76">
+        <f>SUM(Monthly!JT81:KE81)</f>
+        <v>1936788289.3059101</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
-  <ignoredErrors>
-    <ignoredError sqref="AR2:AS76" formulaRange="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:JT81"/>
+  <dimension ref="A1:KJ81"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.453125" customWidth="1"/>
@@ -8921,7 +9197,7 @@
     <col min="260" max="260" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>242</v>
       </c>
@@ -9762,8 +10038,56 @@
       <c r="JT1" t="s">
         <v>428</v>
       </c>
+      <c r="JU1" t="s">
+        <v>430</v>
+      </c>
+      <c r="JV1" t="s">
+        <v>431</v>
+      </c>
+      <c r="JW1" t="s">
+        <v>432</v>
+      </c>
+      <c r="JX1" t="s">
+        <v>433</v>
+      </c>
+      <c r="JY1" t="s">
+        <v>434</v>
+      </c>
+      <c r="JZ1" t="s">
+        <v>435</v>
+      </c>
+      <c r="KA1" t="s">
+        <v>436</v>
+      </c>
+      <c r="KB1" t="s">
+        <v>437</v>
+      </c>
+      <c r="KC1" t="s">
+        <v>438</v>
+      </c>
+      <c r="KD1" t="s">
+        <v>439</v>
+      </c>
+      <c r="KE1" t="s">
+        <v>440</v>
+      </c>
+      <c r="KF1" t="s">
+        <v>441</v>
+      </c>
+      <c r="KG1" t="s">
+        <v>442</v>
+      </c>
+      <c r="KH1" t="s">
+        <v>443</v>
+      </c>
+      <c r="KI1" t="s">
+        <v>444</v>
+      </c>
+      <c r="KJ1" t="s">
+        <v>445</v>
+      </c>
     </row>
-    <row r="2" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>247</v>
       </c>
@@ -10604,8 +10928,56 @@
       <c r="JT2">
         <v>72181656.298989996</v>
       </c>
+      <c r="JU2">
+        <v>70069801.219190016</v>
+      </c>
+      <c r="JV2">
+        <v>143582175.64359999</v>
+      </c>
+      <c r="JW2">
+        <v>52938732.272480004</v>
+      </c>
+      <c r="JX2">
+        <v>112281916</v>
+      </c>
+      <c r="JY2">
+        <v>98029770</v>
+      </c>
+      <c r="JZ2">
+        <v>69368751.387590006</v>
+      </c>
+      <c r="KA2">
+        <v>70901879</v>
+      </c>
+      <c r="KB2">
+        <v>160663622.92181</v>
+      </c>
+      <c r="KC2">
+        <v>74725868</v>
+      </c>
+      <c r="KD2">
+        <v>148838230</v>
+      </c>
+      <c r="KE2">
+        <v>116659084.77904999</v>
+      </c>
+      <c r="KF2">
+        <v>82884429.857529998</v>
+      </c>
+      <c r="KG2">
+        <v>76435200.374779999</v>
+      </c>
+      <c r="KH2">
+        <v>170304587.14585</v>
+      </c>
+      <c r="KI2">
+        <v>51986499.081050001</v>
+      </c>
+      <c r="KJ2">
+        <v>126021855.0554</v>
+      </c>
     </row>
-    <row r="3" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>247</v>
       </c>
@@ -11446,8 +11818,56 @@
       <c r="JT3">
         <v>67157481.569859996</v>
       </c>
+      <c r="JU3">
+        <v>60767545.229309998</v>
+      </c>
+      <c r="JV3">
+        <v>59268764.124530002</v>
+      </c>
+      <c r="JW3">
+        <v>45122583.283529997</v>
+      </c>
+      <c r="JX3">
+        <v>69061051</v>
+      </c>
+      <c r="JY3">
+        <v>62335234</v>
+      </c>
+      <c r="JZ3">
+        <v>61521276.105850004</v>
+      </c>
+      <c r="KA3">
+        <v>65104503</v>
+      </c>
+      <c r="KB3">
+        <v>68913019.168359995</v>
+      </c>
+      <c r="KC3">
+        <v>69640779</v>
+      </c>
+      <c r="KD3">
+        <v>86553216</v>
+      </c>
+      <c r="KE3">
+        <v>75173758.661610007</v>
+      </c>
+      <c r="KF3">
+        <v>73940591.994279996</v>
+      </c>
+      <c r="KG3">
+        <v>67072777.760710001</v>
+      </c>
+      <c r="KH3">
+        <v>65210829.306249999</v>
+      </c>
+      <c r="KI3">
+        <v>44894739.323799998</v>
+      </c>
+      <c r="KJ3">
+        <v>75555868.323609993</v>
+      </c>
     </row>
-    <row r="4" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>247</v>
       </c>
@@ -11748,8 +12168,56 @@
       <c r="JT4">
         <v>1421444.1790700001</v>
       </c>
+      <c r="JU4">
+        <v>1472297</v>
+      </c>
+      <c r="JV4">
+        <v>1515061.2903799999</v>
+      </c>
+      <c r="JW4">
+        <v>1769347.5566100001</v>
+      </c>
+      <c r="JX4">
+        <v>17310061</v>
+      </c>
+      <c r="JY4">
+        <v>3811568</v>
+      </c>
+      <c r="JZ4">
+        <v>4178086.96697</v>
+      </c>
+      <c r="KA4">
+        <v>3401320</v>
+      </c>
+      <c r="KB4">
+        <v>2185793.1885500001</v>
+      </c>
+      <c r="KC4">
+        <v>3466632</v>
+      </c>
+      <c r="KD4">
+        <v>30403430</v>
+      </c>
+      <c r="KE4">
+        <v>3788423.3280799999</v>
+      </c>
+      <c r="KF4">
+        <v>1801950.5704399999</v>
+      </c>
+      <c r="KG4">
+        <v>1636558.8559900001</v>
+      </c>
+      <c r="KH4">
+        <v>1586443.0159100001</v>
+      </c>
+      <c r="KI4">
+        <v>2257812.1984199998</v>
+      </c>
+      <c r="KJ4">
+        <v>18330637.502220001</v>
+      </c>
     </row>
-    <row r="5" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>247</v>
       </c>
@@ -12050,8 +12518,56 @@
       <c r="JT5">
         <v>67193803.692139998</v>
       </c>
+      <c r="JU5">
+        <v>60671240</v>
+      </c>
+      <c r="JV5">
+        <v>58832225.240419999</v>
+      </c>
+      <c r="JW5">
+        <v>62099419.671829998</v>
+      </c>
+      <c r="JX5">
+        <v>59086891</v>
+      </c>
+      <c r="JY5">
+        <v>63078429</v>
+      </c>
+      <c r="JZ5">
+        <v>63230379.702809997</v>
+      </c>
+      <c r="KA5">
+        <v>64906534</v>
+      </c>
+      <c r="KB5">
+        <v>68577625.594919994</v>
+      </c>
+      <c r="KC5">
+        <v>68493489</v>
+      </c>
+      <c r="KD5">
+        <v>57976630</v>
+      </c>
+      <c r="KE5">
+        <v>72971685.831180006</v>
+      </c>
+      <c r="KF5">
+        <v>73167763.903160006</v>
+      </c>
+      <c r="KG5">
+        <v>66757617.322319999</v>
+      </c>
+      <c r="KH5">
+        <v>64686993.920649998</v>
+      </c>
+      <c r="KI5">
+        <v>66305283.525579996</v>
+      </c>
+      <c r="KJ5">
+        <v>62823968.661660001</v>
+      </c>
     </row>
-    <row r="6" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>247</v>
       </c>
@@ -12352,8 +12868,56 @@
       <c r="JT6">
         <v>-276639.51257000002</v>
       </c>
+      <c r="JU6">
+        <v>-332791</v>
+      </c>
+      <c r="JV6">
+        <v>-348676.21638</v>
+      </c>
+      <c r="JW6">
+        <v>-340432.20913999999</v>
+      </c>
+      <c r="JX6">
+        <v>-355728</v>
+      </c>
+      <c r="JY6">
+        <v>-384829</v>
+      </c>
+      <c r="JZ6">
+        <v>-197505.97589999999</v>
+      </c>
+      <c r="KA6">
+        <v>-399744</v>
+      </c>
+      <c r="KB6">
+        <v>-401937.03843000002</v>
+      </c>
+      <c r="KC6">
+        <v>-350714</v>
+      </c>
+      <c r="KD6">
+        <v>-452441</v>
+      </c>
+      <c r="KE6">
+        <v>-446579.55041999999</v>
+      </c>
+      <c r="KF6">
+        <v>-213102.88229000001</v>
+      </c>
+      <c r="KG6">
+        <v>-477524.29667000001</v>
+      </c>
+      <c r="KH6">
+        <v>-336243.76139</v>
+      </c>
+      <c r="KI6">
+        <v>-363040.73813999997</v>
+      </c>
+      <c r="KJ6">
+        <v>-364657.57951000001</v>
+      </c>
     </row>
-    <row r="7" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>247</v>
       </c>
@@ -12654,8 +13218,56 @@
       <c r="JT7">
         <v>-32076.896939999999</v>
       </c>
+      <c r="JU7">
+        <v>-118864</v>
+      </c>
+      <c r="JV7">
+        <v>-71452.987309999997</v>
+      </c>
+      <c r="JW7">
+        <v>-38276.212050000002</v>
+      </c>
+      <c r="JX7">
+        <v>-52978</v>
+      </c>
+      <c r="JY7">
+        <v>-39439</v>
+      </c>
+      <c r="JZ7">
+        <v>-270182.61631999997</v>
+      </c>
+      <c r="KA7">
+        <v>-100018</v>
+      </c>
+      <c r="KB7">
+        <v>-65952.471829999893</v>
+      </c>
+      <c r="KC7">
+        <v>-27754</v>
+      </c>
+      <c r="KD7">
+        <v>-18816</v>
+      </c>
+      <c r="KE7">
+        <v>-17811.861840000001</v>
+      </c>
+      <c r="KF7">
+        <v>-59057.542959999999</v>
+      </c>
+      <c r="KG7">
+        <v>-156907.36905000001</v>
+      </c>
+      <c r="KH7">
+        <v>-106561.10322</v>
+      </c>
+      <c r="KI7">
+        <v>-54043.500890000003</v>
+      </c>
+      <c r="KJ7">
+        <v>-31762.811430000002</v>
+      </c>
     </row>
-    <row r="8" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>247</v>
       </c>
@@ -12956,8 +13568,56 @@
       <c r="JT8">
         <v>-1149049.8918399999</v>
       </c>
+      <c r="JU8">
+        <v>-924338</v>
+      </c>
+      <c r="JV8">
+        <v>-658393.20258000004</v>
+      </c>
+      <c r="JW8">
+        <v>-18367475.52372</v>
+      </c>
+      <c r="JX8">
+        <v>-6927195</v>
+      </c>
+      <c r="JY8">
+        <v>-4130495</v>
+      </c>
+      <c r="JZ8">
+        <v>-5419501.9717100002</v>
+      </c>
+      <c r="KA8">
+        <v>-2703589</v>
+      </c>
+      <c r="KB8">
+        <v>-1382510.10485</v>
+      </c>
+      <c r="KC8">
+        <v>-1940874</v>
+      </c>
+      <c r="KD8">
+        <v>-1355587</v>
+      </c>
+      <c r="KE8">
+        <v>-1121959.0853899999</v>
+      </c>
+      <c r="KF8">
+        <v>-756962.05406999995</v>
+      </c>
+      <c r="KG8">
+        <v>-686966.75188</v>
+      </c>
+      <c r="KH8">
+        <v>-619802.76569999999</v>
+      </c>
+      <c r="KI8">
+        <v>-23251272.161169998</v>
+      </c>
+      <c r="KJ8">
+        <v>-5202317.4493300002</v>
+      </c>
     </row>
-    <row r="9" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>247</v>
       </c>
@@ -13846,8 +14506,56 @@
       <c r="JT9">
         <v>4552758.2383599998</v>
       </c>
+      <c r="JU9">
+        <v>8883145</v>
+      </c>
+      <c r="JV9">
+        <v>83760138.351520002</v>
+      </c>
+      <c r="JW9">
+        <v>7166629.9266799996</v>
+      </c>
+      <c r="JX9">
+        <v>42643644</v>
+      </c>
+      <c r="JY9">
+        <v>35116164</v>
+      </c>
+      <c r="JZ9">
+        <v>7223092.4222800098</v>
+      </c>
+      <c r="KA9">
+        <v>5388191</v>
+      </c>
+      <c r="KB9">
+        <v>91159615.885030001</v>
+      </c>
+      <c r="KC9">
+        <v>4486819</v>
+      </c>
+      <c r="KD9">
+        <v>61578566</v>
+      </c>
+      <c r="KE9">
+        <v>40421661.418250002</v>
+      </c>
+      <c r="KF9">
+        <v>8320971.5108000003</v>
+      </c>
+      <c r="KG9">
+        <v>8722943.3361099996</v>
+      </c>
+      <c r="KH9">
+        <v>104445761.81401999</v>
+      </c>
+      <c r="KI9">
+        <v>6299574.6414299998</v>
+      </c>
+      <c r="KJ9">
+        <v>49965103.73308</v>
+      </c>
     </row>
-    <row r="10" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>247</v>
       </c>
@@ -14688,8 +15396,56 @@
       <c r="JT10">
         <v>922841.05269000004</v>
       </c>
+      <c r="JU10">
+        <v>2424935</v>
+      </c>
+      <c r="JV10">
+        <v>81367502.517560005</v>
+      </c>
+      <c r="JW10">
+        <v>2449812.09669</v>
+      </c>
+      <c r="JX10">
+        <v>39735961</v>
+      </c>
+      <c r="JY10">
+        <v>32407867</v>
+      </c>
+      <c r="JZ10">
+        <v>1475551.3246000099</v>
+      </c>
+      <c r="KA10">
+        <v>1290112</v>
+      </c>
+      <c r="KB10">
+        <v>88641025.716480002</v>
+      </c>
+      <c r="KC10">
+        <v>1352964</v>
+      </c>
+      <c r="KD10">
+        <v>58035618</v>
+      </c>
+      <c r="KE10">
+        <v>35327864.167549998</v>
+      </c>
+      <c r="KF10">
+        <v>1947401.0430900001</v>
+      </c>
+      <c r="KG10">
+        <v>2046737.4240000001</v>
+      </c>
+      <c r="KH10">
+        <v>101783732.34587</v>
+      </c>
+      <c r="KI10">
+        <v>2952897.32754</v>
+      </c>
+      <c r="KJ10">
+        <v>47093026.29501</v>
+      </c>
     </row>
-    <row r="11" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>247</v>
       </c>
@@ -15530,8 +16286,56 @@
       <c r="JT11">
         <v>346.61988000000002</v>
       </c>
+      <c r="JU11">
+        <v>385</v>
+      </c>
+      <c r="JV11">
+        <v>292.59320000000002</v>
+      </c>
+      <c r="JW11">
+        <v>682.78417999999999</v>
+      </c>
+      <c r="JX11">
+        <v>1405</v>
+      </c>
+      <c r="JY11">
+        <v>275</v>
+      </c>
+      <c r="JZ11">
+        <v>1455.76421</v>
+      </c>
+      <c r="KA11">
+        <v>703</v>
+      </c>
+      <c r="KB11">
+        <v>743.14077999999995</v>
+      </c>
+      <c r="KC11">
+        <v>783</v>
+      </c>
+      <c r="KD11">
+        <v>824</v>
+      </c>
+      <c r="KE11">
+        <v>86.995930000000001</v>
+      </c>
+      <c r="KF11">
+        <v>1518.3679500000001</v>
+      </c>
+      <c r="KG11">
+        <v>1111.3094699999999</v>
+      </c>
+      <c r="KH11">
+        <v>667.94063000000006</v>
+      </c>
+      <c r="KI11">
+        <v>289.93736000000001</v>
+      </c>
+      <c r="KJ11">
+        <v>496.44387</v>
+      </c>
     </row>
-    <row r="12" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>247</v>
       </c>
@@ -16012,8 +16816,56 @@
       <c r="JT12">
         <v>3531908.4697599998</v>
       </c>
+      <c r="JU12">
+        <v>6402461</v>
+      </c>
+      <c r="JV12">
+        <v>2344734.8434199998</v>
+      </c>
+      <c r="JW12">
+        <v>4555811.2525300002</v>
+      </c>
+      <c r="JX12">
+        <v>2845315</v>
+      </c>
+      <c r="JY12">
+        <v>2605363</v>
+      </c>
+      <c r="JZ12">
+        <v>5635997.0822999999</v>
+      </c>
+      <c r="KA12">
+        <v>3993393</v>
+      </c>
+      <c r="KB12">
+        <v>2446524.7374</v>
+      </c>
+      <c r="KC12">
+        <v>3015351</v>
+      </c>
+      <c r="KD12">
+        <v>3480224</v>
+      </c>
+      <c r="KE12">
+        <v>5019378.3286199998</v>
+      </c>
+      <c r="KF12">
+        <v>6281020.3044699999</v>
+      </c>
+      <c r="KG12">
+        <v>6626023.2554599997</v>
+      </c>
+      <c r="KH12">
+        <v>2585313.8183900001</v>
+      </c>
+      <c r="KI12">
+        <v>3154966.4870099998</v>
+      </c>
+      <c r="KJ12">
+        <v>2810676.9055900001</v>
+      </c>
     </row>
-    <row r="13" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>247</v>
       </c>
@@ -16386,8 +17238,56 @@
       <c r="JT13">
         <v>97662.096030000001</v>
       </c>
+      <c r="JU13">
+        <v>55364</v>
+      </c>
+      <c r="JV13">
+        <v>47608.397340000003</v>
+      </c>
+      <c r="JW13">
+        <v>160323.79328000001</v>
+      </c>
+      <c r="JX13">
+        <v>60963</v>
+      </c>
+      <c r="JY13">
+        <v>102659</v>
+      </c>
+      <c r="JZ13">
+        <v>110088.25117</v>
+      </c>
+      <c r="KA13">
+        <v>103983</v>
+      </c>
+      <c r="KB13">
+        <v>71322.290370000002</v>
+      </c>
+      <c r="KC13">
+        <v>117721</v>
+      </c>
+      <c r="KD13">
+        <v>61900</v>
+      </c>
+      <c r="KE13">
+        <v>74331.926149999999</v>
+      </c>
+      <c r="KF13">
+        <v>91031.795289999995</v>
+      </c>
+      <c r="KG13">
+        <v>49071.347179999997</v>
+      </c>
+      <c r="KH13">
+        <v>76047.709130000003</v>
+      </c>
+      <c r="KI13">
+        <v>86740.898520000002</v>
+      </c>
+      <c r="KJ13">
+        <v>26795.674770000001</v>
+      </c>
     </row>
-    <row r="14" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>247</v>
       </c>
@@ -16830,7 +17730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>247</v>
       </c>
@@ -17455,8 +18355,56 @@
       <c r="JT15">
         <v>847424.21323999995</v>
       </c>
+      <c r="JU15">
+        <v>613351</v>
+      </c>
+      <c r="JV15">
+        <v>981359.42890000006</v>
+      </c>
+      <c r="JW15">
+        <v>910193.64939999999</v>
+      </c>
+      <c r="JX15">
+        <v>781674</v>
+      </c>
+      <c r="JY15">
+        <v>818464</v>
+      </c>
+      <c r="JZ15">
+        <v>1035521.3419</v>
+      </c>
+      <c r="KA15">
+        <v>374698</v>
+      </c>
+      <c r="KB15">
+        <v>898124.49178000004</v>
+      </c>
+      <c r="KC15">
+        <v>593047</v>
+      </c>
+      <c r="KD15">
+        <v>711368</v>
+      </c>
+      <c r="KE15">
+        <v>1513949.3324599999</v>
+      </c>
+      <c r="KF15">
+        <v>1024597.43351</v>
+      </c>
+      <c r="KG15">
+        <v>578175.49069999997</v>
+      </c>
+      <c r="KH15">
+        <v>1415410.4506999999</v>
+      </c>
+      <c r="KI15">
+        <v>1686706.90114</v>
+      </c>
+      <c r="KJ15">
+        <v>1061915.0591800001</v>
+      </c>
     </row>
-    <row r="16" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>247</v>
       </c>
@@ -18081,8 +19029,56 @@
       <c r="JT16">
         <v>471416.49076999997</v>
       </c>
+      <c r="JU16">
+        <v>419110</v>
+      </c>
+      <c r="JV16">
+        <v>553273.16755000001</v>
+      </c>
+      <c r="JW16">
+        <v>649519.06226999999</v>
+      </c>
+      <c r="JX16">
+        <v>577221</v>
+      </c>
+      <c r="JY16">
+        <v>578372</v>
+      </c>
+      <c r="JZ16">
+        <v>624382.85945999995</v>
+      </c>
+      <c r="KA16">
+        <v>409185</v>
+      </c>
+      <c r="KB16">
+        <v>590987.86841999996</v>
+      </c>
+      <c r="KC16">
+        <v>598270</v>
+      </c>
+      <c r="KD16">
+        <v>706448</v>
+      </c>
+      <c r="KE16">
+        <v>1063664.6991900001</v>
+      </c>
+      <c r="KF16">
+        <v>622866.35245000001</v>
+      </c>
+      <c r="KG16">
+        <v>639479.27795999998</v>
+      </c>
+      <c r="KH16">
+        <v>647996.02558000002</v>
+      </c>
+      <c r="KI16">
+        <v>792185.11581999995</v>
+      </c>
+      <c r="KJ16">
+        <v>500882.99871000001</v>
+      </c>
     </row>
-    <row r="17" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>247</v>
       </c>
@@ -18779,8 +19775,56 @@
       <c r="JT17">
         <v>0</v>
       </c>
+      <c r="JU17">
+        <v>0</v>
+      </c>
+      <c r="JV17">
+        <v>0</v>
+      </c>
+      <c r="JW17">
+        <v>0</v>
+      </c>
+      <c r="JX17">
+        <v>0</v>
+      </c>
+      <c r="JY17">
+        <v>0</v>
+      </c>
+      <c r="JZ17">
+        <v>0</v>
+      </c>
+      <c r="KA17">
+        <v>0</v>
+      </c>
+      <c r="KB17">
+        <v>0</v>
+      </c>
+      <c r="KC17">
+        <v>0</v>
+      </c>
+      <c r="KD17">
+        <v>0</v>
+      </c>
+      <c r="KE17">
+        <v>0</v>
+      </c>
+      <c r="KF17">
+        <v>0</v>
+      </c>
+      <c r="KG17">
+        <v>0</v>
+      </c>
+      <c r="KH17">
+        <v>0</v>
+      </c>
+      <c r="KI17">
+        <v>0</v>
+      </c>
+      <c r="KJ17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>192</v>
       </c>
@@ -19621,8 +20665,56 @@
       <c r="JT18">
         <v>2129295.4993099999</v>
       </c>
+      <c r="JU18">
+        <v>2087942</v>
+      </c>
+      <c r="JV18">
+        <v>2051863.8560599999</v>
+      </c>
+      <c r="JW18">
+        <v>2102991.3665399998</v>
+      </c>
+      <c r="JX18">
+        <v>2056929</v>
+      </c>
+      <c r="JY18">
+        <v>2049458</v>
+      </c>
+      <c r="JZ18">
+        <v>2149659.6006800001</v>
+      </c>
+      <c r="KA18">
+        <v>2176932</v>
+      </c>
+      <c r="KB18">
+        <v>2376137.1373999999</v>
+      </c>
+      <c r="KC18">
+        <v>2374081</v>
+      </c>
+      <c r="KD18">
+        <v>2036959</v>
+      </c>
+      <c r="KE18">
+        <v>2385443.89885</v>
+      </c>
+      <c r="KF18">
+        <v>2253787.4222900001</v>
+      </c>
+      <c r="KG18">
+        <v>2175038.90876</v>
+      </c>
+      <c r="KH18">
+        <v>2176073.0153299998</v>
+      </c>
+      <c r="KI18">
+        <v>2208076.9052499998</v>
+      </c>
+      <c r="KJ18">
+        <v>2135981.7292900002</v>
+      </c>
     </row>
-    <row r="19" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>192</v>
       </c>
@@ -20463,8 +21555,56 @@
       <c r="JT19">
         <v>2129295.4993099999</v>
       </c>
+      <c r="JU19">
+        <v>2087942</v>
+      </c>
+      <c r="JV19">
+        <v>2051863.8560599999</v>
+      </c>
+      <c r="JW19">
+        <v>2102991.3665399998</v>
+      </c>
+      <c r="JX19">
+        <v>2056929</v>
+      </c>
+      <c r="JY19">
+        <v>2049458</v>
+      </c>
+      <c r="JZ19">
+        <v>2149659.6006800001</v>
+      </c>
+      <c r="KA19">
+        <v>2176932</v>
+      </c>
+      <c r="KB19">
+        <v>2376137.1373999999</v>
+      </c>
+      <c r="KC19">
+        <v>2374081</v>
+      </c>
+      <c r="KD19">
+        <v>2036959</v>
+      </c>
+      <c r="KE19">
+        <v>2385443.89885</v>
+      </c>
+      <c r="KF19">
+        <v>2253787.4222900001</v>
+      </c>
+      <c r="KG19">
+        <v>2175038.90876</v>
+      </c>
+      <c r="KH19">
+        <v>2176073.0153299998</v>
+      </c>
+      <c r="KI19">
+        <v>2208076.9052499998</v>
+      </c>
+      <c r="KJ19">
+        <v>2135981.7292900002</v>
+      </c>
     </row>
-    <row r="20" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>194</v>
       </c>
@@ -21305,8 +22445,56 @@
       <c r="JT20">
         <v>1963094.95169</v>
       </c>
+      <c r="JU20">
+        <v>2377507</v>
+      </c>
+      <c r="JV20">
+        <v>1815009.8126699999</v>
+      </c>
+      <c r="JW20">
+        <v>2411329.6732200002</v>
+      </c>
+      <c r="JX20">
+        <v>2077443</v>
+      </c>
+      <c r="JY20">
+        <v>1936239</v>
+      </c>
+      <c r="JZ20">
+        <v>2352820.46269</v>
+      </c>
+      <c r="KA20">
+        <v>2565778</v>
+      </c>
+      <c r="KB20">
+        <v>1787393.82965</v>
+      </c>
+      <c r="KC20">
+        <v>1956472</v>
+      </c>
+      <c r="KD20">
+        <v>2274516</v>
+      </c>
+      <c r="KE20">
+        <v>2827469.07871</v>
+      </c>
+      <c r="KF20">
+        <v>2615464.3428199999</v>
+      </c>
+      <c r="KG20">
+        <v>2074212.63323</v>
+      </c>
+      <c r="KH20">
+        <v>2273065.4068499999</v>
+      </c>
+      <c r="KI20">
+        <v>2354209.4261099999</v>
+      </c>
+      <c r="KJ20">
+        <v>2127077.4608399998</v>
+      </c>
     </row>
-    <row r="21" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>194</v>
       </c>
@@ -22051,8 +23239,56 @@
       <c r="JT21">
         <v>429566.27578000003</v>
       </c>
+      <c r="JU21">
+        <v>622668</v>
+      </c>
+      <c r="JV21">
+        <v>302416.07153999998</v>
+      </c>
+      <c r="JW21">
+        <v>454004.12900000002</v>
+      </c>
+      <c r="JX21">
+        <v>457188</v>
+      </c>
+      <c r="JY21">
+        <v>381340</v>
+      </c>
+      <c r="JZ21">
+        <v>463846.87891999999</v>
+      </c>
+      <c r="KA21">
+        <v>532521</v>
+      </c>
+      <c r="KB21">
+        <v>527302.09722</v>
+      </c>
+      <c r="KC21">
+        <v>485040</v>
+      </c>
+      <c r="KD21">
+        <v>455904</v>
+      </c>
+      <c r="KE21">
+        <v>891268.27307999996</v>
+      </c>
+      <c r="KF21">
+        <v>545803.26818000001</v>
+      </c>
+      <c r="KG21">
+        <v>385417.72681999998</v>
+      </c>
+      <c r="KH21">
+        <v>424891.13679000002</v>
+      </c>
+      <c r="KI21">
+        <v>409577.97622000001</v>
+      </c>
+      <c r="KJ21">
+        <v>528004.59109</v>
+      </c>
     </row>
-    <row r="22" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>194</v>
       </c>
@@ -22893,8 +24129,56 @@
       <c r="JT22">
         <v>95914.341149999993</v>
       </c>
+      <c r="JU22">
+        <v>65235</v>
+      </c>
+      <c r="JV22">
+        <v>73430.558109999998</v>
+      </c>
+      <c r="JW22">
+        <v>75213.986130000005</v>
+      </c>
+      <c r="JX22">
+        <v>55626</v>
+      </c>
+      <c r="JY22">
+        <v>46173</v>
+      </c>
+      <c r="JZ22">
+        <v>89446.835489999998</v>
+      </c>
+      <c r="KA22">
+        <v>79332</v>
+      </c>
+      <c r="KB22">
+        <v>99037.868570000006</v>
+      </c>
+      <c r="KC22">
+        <v>133669</v>
+      </c>
+      <c r="KD22">
+        <v>91642</v>
+      </c>
+      <c r="KE22">
+        <v>463799.26415</v>
+      </c>
+      <c r="KF22">
+        <v>167331.24755</v>
+      </c>
+      <c r="KG22">
+        <v>75488.638680000004</v>
+      </c>
+      <c r="KH22">
+        <v>106173.89255999999</v>
+      </c>
+      <c r="KI22">
+        <v>49457.489459999997</v>
+      </c>
+      <c r="KJ22">
+        <v>66104.795370000007</v>
+      </c>
     </row>
-    <row r="23" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>194</v>
       </c>
@@ -23735,8 +25019,56 @@
       <c r="JT23">
         <v>333651.93462999997</v>
       </c>
+      <c r="JU23">
+        <v>557433</v>
+      </c>
+      <c r="JV23">
+        <v>228985.51342999999</v>
+      </c>
+      <c r="JW23">
+        <v>378790.14286999998</v>
+      </c>
+      <c r="JX23">
+        <v>401562</v>
+      </c>
+      <c r="JY23">
+        <v>335167</v>
+      </c>
+      <c r="JZ23">
+        <v>374400.04343000002</v>
+      </c>
+      <c r="KA23">
+        <v>453189</v>
+      </c>
+      <c r="KB23">
+        <v>428264.22865</v>
+      </c>
+      <c r="KC23">
+        <v>351371</v>
+      </c>
+      <c r="KD23">
+        <v>364262</v>
+      </c>
+      <c r="KE23">
+        <v>427469.00893000001</v>
+      </c>
+      <c r="KF23">
+        <v>378472.02062999998</v>
+      </c>
+      <c r="KG23">
+        <v>309929.08814000001</v>
+      </c>
+      <c r="KH23">
+        <v>318717.24423000001</v>
+      </c>
+      <c r="KI23">
+        <v>360120.48676</v>
+      </c>
+      <c r="KJ23">
+        <v>461899.79571999999</v>
+      </c>
     </row>
-    <row r="24" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>194</v>
       </c>
@@ -24481,8 +25813,56 @@
       <c r="JT24">
         <v>1533528.67591</v>
       </c>
+      <c r="JU24">
+        <v>1754839</v>
+      </c>
+      <c r="JV24">
+        <v>1512593.74113</v>
+      </c>
+      <c r="JW24">
+        <v>1957325.54422</v>
+      </c>
+      <c r="JX24">
+        <v>1620255</v>
+      </c>
+      <c r="JY24">
+        <v>1554899</v>
+      </c>
+      <c r="JZ24">
+        <v>1888973.5837699999</v>
+      </c>
+      <c r="KA24">
+        <v>2033257</v>
+      </c>
+      <c r="KB24">
+        <v>1260091.7324300001</v>
+      </c>
+      <c r="KC24">
+        <v>1471432</v>
+      </c>
+      <c r="KD24">
+        <v>1818612</v>
+      </c>
+      <c r="KE24">
+        <v>1936200.8056300001</v>
+      </c>
+      <c r="KF24">
+        <v>2069661.07464</v>
+      </c>
+      <c r="KG24">
+        <v>1688794.9064100001</v>
+      </c>
+      <c r="KH24">
+        <v>1848174.27006</v>
+      </c>
+      <c r="KI24">
+        <v>1944631.44989</v>
+      </c>
+      <c r="KJ24">
+        <v>1599072.8697500001</v>
+      </c>
     </row>
-    <row r="25" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>194</v>
       </c>
@@ -25323,8 +26703,56 @@
       <c r="JT25">
         <v>516160.89184</v>
       </c>
+      <c r="JU25">
+        <v>557569</v>
+      </c>
+      <c r="JV25">
+        <v>459742.15544</v>
+      </c>
+      <c r="JW25">
+        <v>811230.22806999995</v>
+      </c>
+      <c r="JX25">
+        <v>605604</v>
+      </c>
+      <c r="JY25">
+        <v>552084</v>
+      </c>
+      <c r="JZ25">
+        <v>746555.38035999995</v>
+      </c>
+      <c r="KA25">
+        <v>862213</v>
+      </c>
+      <c r="KB25">
+        <v>586489.96106999996</v>
+      </c>
+      <c r="KC25">
+        <v>537567</v>
+      </c>
+      <c r="KD25">
+        <v>673466</v>
+      </c>
+      <c r="KE25">
+        <v>642857.30709999998</v>
+      </c>
+      <c r="KF25">
+        <v>862175.19461999997</v>
+      </c>
+      <c r="KG25">
+        <v>579163.49638000003</v>
+      </c>
+      <c r="KH25">
+        <v>569182.25341</v>
+      </c>
+      <c r="KI25">
+        <v>630165.87347999995</v>
+      </c>
+      <c r="KJ25">
+        <v>536562.61416</v>
+      </c>
     </row>
-    <row r="26" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>194</v>
       </c>
@@ -26165,8 +27593,56 @@
       <c r="JT26">
         <v>1017367.7840700001</v>
       </c>
+      <c r="JU26">
+        <v>1197270</v>
+      </c>
+      <c r="JV26">
+        <v>1052851.5856900001</v>
+      </c>
+      <c r="JW26">
+        <v>1146095.3161500001</v>
+      </c>
+      <c r="JX26">
+        <v>1014651</v>
+      </c>
+      <c r="JY26">
+        <v>1002815</v>
+      </c>
+      <c r="JZ26">
+        <v>1142418.2034100001</v>
+      </c>
+      <c r="KA26">
+        <v>1171044</v>
+      </c>
+      <c r="KB26">
+        <v>673601.77136000001</v>
+      </c>
+      <c r="KC26">
+        <v>933865</v>
+      </c>
+      <c r="KD26">
+        <v>1145146</v>
+      </c>
+      <c r="KE26">
+        <v>1293343.49853</v>
+      </c>
+      <c r="KF26">
+        <v>1207485.88002</v>
+      </c>
+      <c r="KG26">
+        <v>1109631.4100299999</v>
+      </c>
+      <c r="KH26">
+        <v>1278992.0166499999</v>
+      </c>
+      <c r="KI26">
+        <v>1314465.57641</v>
+      </c>
+      <c r="KJ26">
+        <v>1062510.25559</v>
+      </c>
     </row>
-    <row r="27" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>293</v>
       </c>
@@ -27007,8 +28483,56 @@
       <c r="JT27">
         <v>41714950.057340004</v>
       </c>
+      <c r="JU27">
+        <v>53978498</v>
+      </c>
+      <c r="JV27">
+        <v>52770353.200390004</v>
+      </c>
+      <c r="JW27">
+        <v>56460431.557520002</v>
+      </c>
+      <c r="JX27">
+        <v>53049585</v>
+      </c>
+      <c r="JY27">
+        <v>56097690</v>
+      </c>
+      <c r="JZ27">
+        <v>54560910.92977</v>
+      </c>
+      <c r="KA27">
+        <v>58417088</v>
+      </c>
+      <c r="KB27">
+        <v>55837879.080119997</v>
+      </c>
+      <c r="KC27">
+        <v>70165593</v>
+      </c>
+      <c r="KD27">
+        <v>54933393</v>
+      </c>
+      <c r="KE27">
+        <v>75580639.250880003</v>
+      </c>
+      <c r="KF27">
+        <v>43203787.660300002</v>
+      </c>
+      <c r="KG27">
+        <v>55609862.486830004</v>
+      </c>
+      <c r="KH27">
+        <v>47204295.697250001</v>
+      </c>
+      <c r="KI27">
+        <v>56104909.590599999</v>
+      </c>
+      <c r="KJ27">
+        <v>56068469.179669999</v>
+      </c>
     </row>
-    <row r="28" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>293</v>
       </c>
@@ -27849,8 +29373,56 @@
       <c r="JT28">
         <v>27117104.01588</v>
       </c>
+      <c r="JU28">
+        <v>40009898</v>
+      </c>
+      <c r="JV28">
+        <v>39106958.43581</v>
+      </c>
+      <c r="JW28">
+        <v>39737601.407909997</v>
+      </c>
+      <c r="JX28">
+        <v>40560073</v>
+      </c>
+      <c r="JY28">
+        <v>42477120</v>
+      </c>
+      <c r="JZ28">
+        <v>37958894.38442</v>
+      </c>
+      <c r="KA28">
+        <v>44265382</v>
+      </c>
+      <c r="KB28">
+        <v>40398474.955820002</v>
+      </c>
+      <c r="KC28">
+        <v>50613275</v>
+      </c>
+      <c r="KD28">
+        <v>39215764</v>
+      </c>
+      <c r="KE28">
+        <v>59126061.981969997</v>
+      </c>
+      <c r="KF28">
+        <v>32371648.850219999</v>
+      </c>
+      <c r="KG28">
+        <v>45636715.800489999</v>
+      </c>
+      <c r="KH28">
+        <v>38774821.280380003</v>
+      </c>
+      <c r="KI28">
+        <v>42142991.205480002</v>
+      </c>
+      <c r="KJ28">
+        <v>44501110.193120003</v>
+      </c>
     </row>
-    <row r="29" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>293</v>
       </c>
@@ -28367,8 +29939,56 @@
       <c r="JT29">
         <v>46576252.442419998</v>
       </c>
+      <c r="JU29">
+        <v>47790761</v>
+      </c>
+      <c r="JV29">
+        <v>47924340.94184</v>
+      </c>
+      <c r="JW29">
+        <v>49216257.806369998</v>
+      </c>
+      <c r="JX29">
+        <v>50509596</v>
+      </c>
+      <c r="JY29">
+        <v>50708334</v>
+      </c>
+      <c r="JZ29">
+        <v>49879798.619000003</v>
+      </c>
+      <c r="KA29">
+        <v>52719199</v>
+      </c>
+      <c r="KB29">
+        <v>52109530.863300003</v>
+      </c>
+      <c r="KC29">
+        <v>57158644</v>
+      </c>
+      <c r="KD29">
+        <v>49231777</v>
+      </c>
+      <c r="KE29">
+        <v>50133422.520439997</v>
+      </c>
+      <c r="KF29">
+        <v>54219617.713760003</v>
+      </c>
+      <c r="KG29">
+        <v>53432471.780440003</v>
+      </c>
+      <c r="KH29">
+        <v>48886414.999140002</v>
+      </c>
+      <c r="KI29">
+        <v>51402008.585890003</v>
+      </c>
+      <c r="KJ29">
+        <v>53822739.22484</v>
+      </c>
     </row>
-    <row r="30" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>293</v>
       </c>
@@ -28885,8 +30505,56 @@
       <c r="JT30">
         <v>7086159.5102899997</v>
       </c>
+      <c r="JU30">
+        <v>21376684</v>
+      </c>
+      <c r="JV30">
+        <v>22109849.239750002</v>
+      </c>
+      <c r="JW30">
+        <v>22086839.830279998</v>
+      </c>
+      <c r="JX30">
+        <v>23065805</v>
+      </c>
+      <c r="JY30">
+        <v>24483367</v>
+      </c>
+      <c r="JZ30">
+        <v>25096352.884660002</v>
+      </c>
+      <c r="KA30">
+        <v>23135145</v>
+      </c>
+      <c r="KB30">
+        <v>21534255.301509999</v>
+      </c>
+      <c r="KC30">
+        <v>20072942</v>
+      </c>
+      <c r="KD30">
+        <v>21628785</v>
+      </c>
+      <c r="KE30">
+        <v>36051109.996480003</v>
+      </c>
+      <c r="KF30">
+        <v>6871190.4906599997</v>
+      </c>
+      <c r="KG30">
+        <v>21731670.839979999</v>
+      </c>
+      <c r="KH30">
+        <v>23008695.152070001</v>
+      </c>
+      <c r="KI30">
+        <v>24392768.404959999</v>
+      </c>
+      <c r="KJ30">
+        <v>24039065.193059999</v>
+      </c>
     </row>
-    <row r="31" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>293</v>
       </c>
@@ -29403,8 +31071,56 @@
       <c r="JT31">
         <v>-26545307.936829999</v>
       </c>
+      <c r="JU31">
+        <v>-29157547</v>
+      </c>
+      <c r="JV31">
+        <v>-30927231.745779999</v>
+      </c>
+      <c r="JW31">
+        <v>-31565496.228739999</v>
+      </c>
+      <c r="JX31">
+        <v>-33015328</v>
+      </c>
+      <c r="JY31">
+        <v>-32714581</v>
+      </c>
+      <c r="JZ31">
+        <v>-37017257.119240001</v>
+      </c>
+      <c r="KA31">
+        <v>-31588962</v>
+      </c>
+      <c r="KB31">
+        <v>-33245311.20899</v>
+      </c>
+      <c r="KC31">
+        <v>-26618311</v>
+      </c>
+      <c r="KD31">
+        <v>-31644798</v>
+      </c>
+      <c r="KE31">
+        <v>-27058470.534949999</v>
+      </c>
+      <c r="KF31">
+        <v>-28719159.354200002</v>
+      </c>
+      <c r="KG31">
+        <v>-29527426.819929998</v>
+      </c>
+      <c r="KH31">
+        <v>-33120288.870829999</v>
+      </c>
+      <c r="KI31">
+        <v>-33651785.78537</v>
+      </c>
+      <c r="KJ31">
+        <v>-33360694.224780001</v>
+      </c>
     </row>
-    <row r="32" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>293</v>
       </c>
@@ -29955,7 +31671,7 @@
         <v>451.02665000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>293</v>
       </c>
@@ -30796,8 +32512,56 @@
       <c r="JT33">
         <v>3991463.0462099998</v>
       </c>
+      <c r="JU33">
+        <v>4136848</v>
+      </c>
+      <c r="JV33">
+        <v>4347494.8028300004</v>
+      </c>
+      <c r="JW33">
+        <v>4724270.6858799998</v>
+      </c>
+      <c r="JX33">
+        <v>3071581</v>
+      </c>
+      <c r="JY33">
+        <v>4339358</v>
+      </c>
+      <c r="JZ33">
+        <v>4978498.3149800003</v>
+      </c>
+      <c r="KA33">
+        <v>5384356</v>
+      </c>
+      <c r="KB33">
+        <v>5472960.8234299999</v>
+      </c>
+      <c r="KC33">
+        <v>8072134</v>
+      </c>
+      <c r="KD33">
+        <v>6217686</v>
+      </c>
+      <c r="KE33">
+        <v>7000627.3189300001</v>
+      </c>
+      <c r="KF33">
+        <v>4075370.0970600001</v>
+      </c>
+      <c r="KG33">
+        <v>4021212.4124199999</v>
+      </c>
+      <c r="KH33">
+        <v>4910042.1600099998</v>
+      </c>
+      <c r="KI33">
+        <v>5414937.6729199998</v>
+      </c>
+      <c r="KJ33">
+        <v>3409187.6927899998</v>
+      </c>
     </row>
-    <row r="34" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>293</v>
       </c>
@@ -31638,8 +33402,56 @@
       <c r="JT34">
         <v>1057756.69151</v>
       </c>
+      <c r="JU34">
+        <v>2095519</v>
+      </c>
+      <c r="JV34">
+        <v>2119275.6263199998</v>
+      </c>
+      <c r="JW34">
+        <v>1969914.8244099999</v>
+      </c>
+      <c r="JX34">
+        <v>2148761</v>
+      </c>
+      <c r="JY34">
+        <v>2180840</v>
+      </c>
+      <c r="JZ34">
+        <v>2357041.72596</v>
+      </c>
+      <c r="KA34">
+        <v>2434047</v>
+      </c>
+      <c r="KB34">
+        <v>2444436.4733000002</v>
+      </c>
+      <c r="KC34">
+        <v>2544951</v>
+      </c>
+      <c r="KD34">
+        <v>2551728</v>
+      </c>
+      <c r="KE34">
+        <v>3525048.4998300001</v>
+      </c>
+      <c r="KF34">
+        <v>1201384.0344400001</v>
+      </c>
+      <c r="KG34">
+        <v>2170291.4227200001</v>
+      </c>
+      <c r="KH34">
+        <v>2266143.4944099998</v>
+      </c>
+      <c r="KI34">
+        <v>2294128.37268</v>
+      </c>
+      <c r="KJ34">
+        <v>2299749.8256100002</v>
+      </c>
     </row>
-    <row r="35" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>293</v>
       </c>
@@ -32480,8 +34292,56 @@
       <c r="JT35">
         <v>237.20928000000001</v>
       </c>
+      <c r="JU35">
+        <v>244</v>
+      </c>
+      <c r="JV35">
+        <v>320.86703</v>
+      </c>
+      <c r="JW35">
+        <v>369.55324000000002</v>
+      </c>
+      <c r="JX35">
+        <v>451</v>
+      </c>
+      <c r="JY35">
+        <v>380</v>
+      </c>
+      <c r="JZ35">
+        <v>375.59638999999999</v>
+      </c>
+      <c r="KA35">
+        <v>312</v>
+      </c>
+      <c r="KB35">
+        <v>228.40602999999999</v>
+      </c>
+      <c r="KC35">
+        <v>336</v>
+      </c>
+      <c r="KD35">
+        <v>122</v>
+      </c>
+      <c r="KE35">
+        <v>289.27881000000002</v>
+      </c>
+      <c r="KF35">
+        <v>351.04102999999998</v>
+      </c>
+      <c r="KG35">
+        <v>218.97506000000001</v>
+      </c>
+      <c r="KH35">
+        <v>250.44011</v>
+      </c>
+      <c r="KI35">
+        <v>177.63588999999999</v>
+      </c>
+      <c r="KJ35">
+        <v>293.70236</v>
+      </c>
     </row>
-    <row r="36" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>293</v>
       </c>
@@ -33322,8 +35182,56 @@
       <c r="JT36">
         <v>539636.98508999997</v>
       </c>
+      <c r="JU36">
+        <v>502671</v>
+      </c>
+      <c r="JV36">
+        <v>592002.68655999994</v>
+      </c>
+      <c r="JW36">
+        <v>562265.05168000003</v>
+      </c>
+      <c r="JX36">
+        <v>34710</v>
+      </c>
+      <c r="JY36">
+        <v>591750</v>
+      </c>
+      <c r="JZ36">
+        <v>644780.71969000006</v>
+      </c>
+      <c r="KA36">
+        <v>708763</v>
+      </c>
+      <c r="KB36">
+        <v>767291.80541999999</v>
+      </c>
+      <c r="KC36">
+        <v>829430</v>
+      </c>
+      <c r="KD36">
+        <v>1312208</v>
+      </c>
+      <c r="KE36">
+        <v>604903.87864000001</v>
+      </c>
+      <c r="KF36">
+        <v>618570.08625000005</v>
+      </c>
+      <c r="KG36">
+        <v>541264.03437000001</v>
+      </c>
+      <c r="KH36">
+        <v>579242.81842000003</v>
+      </c>
+      <c r="KI36">
+        <v>649316.31750999996</v>
+      </c>
+      <c r="KJ36">
+        <v>32055.509890000001</v>
+      </c>
     </row>
-    <row r="37" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>293</v>
       </c>
@@ -33406,7 +35314,7 @@
         <v>-217</v>
       </c>
     </row>
-    <row r="38" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>293</v>
       </c>
@@ -34247,8 +36155,56 @@
       <c r="JT38">
         <v>1308342.0079000001</v>
       </c>
+      <c r="JU38">
+        <v>1176485</v>
+      </c>
+      <c r="JV38">
+        <v>1208626.32742</v>
+      </c>
+      <c r="JW38">
+        <v>978718.90313999995</v>
+      </c>
+      <c r="JX38">
+        <v>394295</v>
+      </c>
+      <c r="JY38">
+        <v>939932</v>
+      </c>
+      <c r="JZ38">
+        <v>711995.24529999995</v>
+      </c>
+      <c r="KA38">
+        <v>1469082</v>
+      </c>
+      <c r="KB38">
+        <v>1475937.15081</v>
+      </c>
+      <c r="KC38">
+        <v>1511557</v>
+      </c>
+      <c r="KD38">
+        <v>1627710</v>
+      </c>
+      <c r="KE38">
+        <v>1601168.64118</v>
+      </c>
+      <c r="KF38">
+        <v>1193593.1658300001</v>
+      </c>
+      <c r="KG38">
+        <v>1071277.8889899999</v>
+      </c>
+      <c r="KH38">
+        <v>1687710.04455</v>
+      </c>
+      <c r="KI38">
+        <v>1263149.5190699999</v>
+      </c>
+      <c r="KJ38">
+        <v>667548.68998999998</v>
+      </c>
     </row>
-    <row r="39" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>293</v>
       </c>
@@ -35089,8 +37045,56 @@
       <c r="JT39">
         <v>970310.61655000004</v>
       </c>
+      <c r="JU39">
+        <v>267227</v>
+      </c>
+      <c r="JV39">
+        <v>360858.26286999998</v>
+      </c>
+      <c r="JW39">
+        <v>372821.83354999998</v>
+      </c>
+      <c r="JX39">
+        <v>422798</v>
+      </c>
+      <c r="JY39">
+        <v>548215</v>
+      </c>
+      <c r="JZ39">
+        <v>658315.89</v>
+      </c>
+      <c r="KA39">
+        <v>700337</v>
+      </c>
+      <c r="KB39">
+        <v>648725.61210000003</v>
+      </c>
+      <c r="KC39">
+        <v>2410513</v>
+      </c>
+      <c r="KD39">
+        <v>647295</v>
+      </c>
+      <c r="KE39">
+        <v>604961.40232999995</v>
+      </c>
+      <c r="KF39">
+        <v>956521.47253999999</v>
+      </c>
+      <c r="KG39">
+        <v>190621.56255999999</v>
+      </c>
+      <c r="KH39">
+        <v>319083.75042</v>
+      </c>
+      <c r="KI39">
+        <v>383558.48605000001</v>
+      </c>
+      <c r="KJ39">
+        <v>345367.93685</v>
+      </c>
     </row>
-    <row r="40" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>293</v>
       </c>
@@ -35139,8 +37143,56 @@
       <c r="JT40">
         <v>0</v>
       </c>
+      <c r="JU40">
+        <v>0</v>
+      </c>
+      <c r="JV40">
+        <v>0</v>
+      </c>
+      <c r="JW40">
+        <v>0</v>
+      </c>
+      <c r="JX40">
+        <v>0</v>
+      </c>
+      <c r="JY40">
+        <v>0</v>
+      </c>
+      <c r="JZ40">
+        <v>0</v>
+      </c>
+      <c r="KA40">
+        <v>0</v>
+      </c>
+      <c r="KB40">
+        <v>0</v>
+      </c>
+      <c r="KC40">
+        <v>0</v>
+      </c>
+      <c r="KD40">
+        <v>0</v>
+      </c>
+      <c r="KE40">
+        <v>0</v>
+      </c>
+      <c r="KF40">
+        <v>0</v>
+      </c>
+      <c r="KG40">
+        <v>0</v>
+      </c>
+      <c r="KH40">
+        <v>0</v>
+      </c>
+      <c r="KI40">
+        <v>0</v>
+      </c>
+      <c r="KJ40">
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>293</v>
       </c>
@@ -35151,7 +37203,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="42" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>293</v>
       </c>
@@ -35992,8 +38044,56 @@
       <c r="JT42">
         <v>56180.774340000004</v>
       </c>
+      <c r="JU42">
+        <v>56374</v>
+      </c>
+      <c r="JV42">
+        <v>29659.61953</v>
+      </c>
+      <c r="JW42">
+        <v>36836.808989999998</v>
+      </c>
+      <c r="JX42">
+        <v>33270</v>
+      </c>
+      <c r="JY42">
+        <v>42793</v>
+      </c>
+      <c r="JZ42">
+        <v>36990.74667</v>
+      </c>
+      <c r="KA42">
+        <v>37451</v>
+      </c>
+      <c r="KB42">
+        <v>48355.15971</v>
+      </c>
+      <c r="KC42">
+        <v>53932</v>
+      </c>
+      <c r="KD42">
+        <v>36293</v>
+      </c>
+      <c r="KE42">
+        <v>36774.717539999998</v>
+      </c>
+      <c r="KF42">
+        <v>64037.650119999998</v>
+      </c>
+      <c r="KG42">
+        <v>64.931439999999995</v>
+      </c>
+      <c r="KH42">
+        <v>31030.128540000002</v>
+      </c>
+      <c r="KI42">
+        <v>32917.961759999998</v>
+      </c>
+      <c r="KJ42">
+        <v>29547.751929999999</v>
+      </c>
     </row>
-    <row r="43" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>293</v>
       </c>
@@ -36834,8 +38934,56 @@
       <c r="JT43">
         <v>50110.96357</v>
       </c>
+      <c r="JU43">
+        <v>38014</v>
+      </c>
+      <c r="JV43">
+        <v>36626.833420000003</v>
+      </c>
+      <c r="JW43">
+        <v>37981.588589999999</v>
+      </c>
+      <c r="JX43">
+        <v>37232</v>
+      </c>
+      <c r="JY43">
+        <v>35251</v>
+      </c>
+      <c r="JZ43">
+        <v>32827.650869999998</v>
+      </c>
+      <c r="KA43">
+        <v>34242</v>
+      </c>
+      <c r="KB43">
+        <v>39661.453500000003</v>
+      </c>
+      <c r="KC43">
+        <v>35924</v>
+      </c>
+      <c r="KD43">
+        <v>42171</v>
+      </c>
+      <c r="KE43">
+        <v>32593.613099999999</v>
+      </c>
+      <c r="KF43">
+        <v>40845.585310000002</v>
+      </c>
+      <c r="KG43">
+        <v>35593.369120000003</v>
+      </c>
+      <c r="KH43">
+        <v>26481.559679999998</v>
+      </c>
+      <c r="KI43">
+        <v>30828.75229</v>
+      </c>
+      <c r="KJ43">
+        <v>34587.243920000001</v>
+      </c>
     </row>
-    <row r="44" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>293</v>
       </c>
@@ -37577,8 +39725,56 @@
       <c r="JT44">
         <v>8870.9563699999999</v>
       </c>
+      <c r="JU44">
+        <v>0</v>
+      </c>
+      <c r="JV44">
+        <v>0</v>
+      </c>
+      <c r="JW44">
+        <v>765216.22387999995</v>
+      </c>
+      <c r="JX44">
+        <v>0</v>
+      </c>
+      <c r="JY44">
+        <v>0</v>
+      </c>
+      <c r="JZ44">
+        <v>535988.14450000005</v>
+      </c>
+      <c r="KA44">
+        <v>0</v>
+      </c>
+      <c r="KB44">
+        <v>48227.27648</v>
+      </c>
+      <c r="KC44">
+        <v>685163</v>
+      </c>
+      <c r="KD44">
+        <v>0</v>
+      </c>
+      <c r="KE44">
+        <v>594796.53029999998</v>
+      </c>
+      <c r="KF44">
+        <v>17.552620000000001</v>
+      </c>
+      <c r="KG44">
+        <v>11880.228160000001</v>
+      </c>
+      <c r="KH44">
+        <v>0</v>
+      </c>
+      <c r="KI44">
+        <v>760718.36806999997</v>
+      </c>
+      <c r="KJ44">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>293</v>
       </c>
@@ -38419,8 +40615,56 @@
       <c r="JT45">
         <v>1758126.2206900001</v>
       </c>
+      <c r="JU45">
+        <v>2720</v>
+      </c>
+      <c r="JV45">
+        <v>543.89990999999998</v>
+      </c>
+      <c r="JW45">
+        <v>1905311.94257</v>
+      </c>
+      <c r="JX45">
+        <v>1315</v>
+      </c>
+      <c r="JY45">
+        <v>966</v>
+      </c>
+      <c r="JZ45">
+        <v>2175897.65717</v>
+      </c>
+      <c r="KA45">
+        <v>1061</v>
+      </c>
+      <c r="KB45">
+        <v>16494.784650000001</v>
+      </c>
+      <c r="KC45">
+        <v>2018208</v>
+      </c>
+      <c r="KD45">
+        <v>1076</v>
+      </c>
+      <c r="KE45">
+        <v>116715.08643</v>
+      </c>
+      <c r="KF45">
+        <v>2063913.1085699999</v>
+      </c>
+      <c r="KG45">
+        <v>801.86071000000004</v>
+      </c>
+      <c r="KH45">
+        <v>21835.771959999998</v>
+      </c>
+      <c r="KI45">
+        <v>1887025.879</v>
+      </c>
+      <c r="KJ45">
+        <v>5483.1188899999997</v>
+      </c>
     </row>
-    <row r="46" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>293</v>
       </c>
@@ -38685,8 +40929,56 @@
       <c r="JT46">
         <v>216642.09917</v>
       </c>
+      <c r="JU46">
+        <v>167271</v>
+      </c>
+      <c r="JV46">
+        <v>155329.19646000001</v>
+      </c>
+      <c r="JW46">
+        <v>154570.80413999999</v>
+      </c>
+      <c r="JX46">
+        <v>157410</v>
+      </c>
+      <c r="JY46">
+        <v>174607</v>
+      </c>
+      <c r="JZ46">
+        <v>226809.88295999999</v>
+      </c>
+      <c r="KA46">
+        <v>245416</v>
+      </c>
+      <c r="KB46">
+        <v>226800.13725999999</v>
+      </c>
+      <c r="KC46">
+        <v>226257</v>
+      </c>
+      <c r="KD46">
+        <v>183553</v>
+      </c>
+      <c r="KE46">
+        <v>212406.70105999999</v>
+      </c>
+      <c r="KF46">
+        <v>244223.75099999999</v>
+      </c>
+      <c r="KG46">
+        <v>175945.44055</v>
+      </c>
+      <c r="KH46">
+        <v>142776.13435000001</v>
+      </c>
+      <c r="KI46">
+        <v>144373.95937999999</v>
+      </c>
+      <c r="KJ46">
+        <v>179242.30987</v>
+      </c>
     </row>
-    <row r="47" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>293</v>
       </c>
@@ -39527,8 +41819,56 @@
       <c r="JT47">
         <v>7630315.3501500003</v>
       </c>
+      <c r="JU47">
+        <v>8723562</v>
+      </c>
+      <c r="JV47">
+        <v>7996821.6186100002</v>
+      </c>
+      <c r="JW47">
+        <v>6895355.8931099996</v>
+      </c>
+      <c r="JX47">
+        <v>8112549</v>
+      </c>
+      <c r="JY47">
+        <v>7884462</v>
+      </c>
+      <c r="JZ47">
+        <v>7918424.9396900004</v>
+      </c>
+      <c r="KA47">
+        <v>7476761</v>
+      </c>
+      <c r="KB47">
+        <v>8346739.3769899998</v>
+      </c>
+      <c r="KC47">
+        <v>8071904</v>
+      </c>
+      <c r="KD47">
+        <v>8314502</v>
+      </c>
+      <c r="KE47">
+        <v>7834320.1410999997</v>
+      </c>
+      <c r="KF47">
+        <v>3525862.0483300001</v>
+      </c>
+      <c r="KG47">
+        <v>4827621.48398</v>
+      </c>
+      <c r="KH47">
+        <v>2200413.23857</v>
+      </c>
+      <c r="KI47">
+        <v>3750067.1392199998</v>
+      </c>
+      <c r="KJ47">
+        <v>6908211.0524899997</v>
+      </c>
     </row>
-    <row r="48" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>293</v>
       </c>
@@ -39757,8 +42097,56 @@
       <c r="JT48">
         <v>277602.36747</v>
       </c>
+      <c r="JU48">
+        <v>327122</v>
+      </c>
+      <c r="JV48">
+        <v>326396.41353999998</v>
+      </c>
+      <c r="JW48">
+        <v>278718.27130000002</v>
+      </c>
+      <c r="JX48">
+        <v>325448</v>
+      </c>
+      <c r="JY48">
+        <v>310368</v>
+      </c>
+      <c r="JZ48">
+        <v>318718.88903000002</v>
+      </c>
+      <c r="KA48">
+        <v>296840</v>
+      </c>
+      <c r="KB48">
+        <v>332543.06251999998</v>
+      </c>
+      <c r="KC48">
+        <v>318730</v>
+      </c>
+      <c r="KD48">
+        <v>345169</v>
+      </c>
+      <c r="KE48">
+        <v>447696.47110999998</v>
+      </c>
+      <c r="KF48">
+        <v>593011.59169999999</v>
+      </c>
+      <c r="KG48">
+        <v>164786.37766</v>
+      </c>
+      <c r="KH48">
+        <v>219208.46197999999</v>
+      </c>
+      <c r="KI48">
+        <v>201599.55343</v>
+      </c>
+      <c r="KJ48">
+        <v>375362.24028000003</v>
+      </c>
     </row>
-    <row r="49" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>293</v>
       </c>
@@ -39987,8 +42375,56 @@
       <c r="JT49">
         <v>182529.30949000001</v>
       </c>
+      <c r="JU49">
+        <v>136504</v>
+      </c>
+      <c r="JV49">
+        <v>126298.66885</v>
+      </c>
+      <c r="JW49">
+        <v>136324.04243999999</v>
+      </c>
+      <c r="JX49">
+        <v>128744</v>
+      </c>
+      <c r="JY49">
+        <v>121217</v>
+      </c>
+      <c r="JZ49">
+        <v>109117.92346999999</v>
+      </c>
+      <c r="KA49">
+        <v>118664</v>
+      </c>
+      <c r="KB49">
+        <v>143065.24997</v>
+      </c>
+      <c r="KC49">
+        <v>130799</v>
+      </c>
+      <c r="KD49">
+        <v>148616</v>
+      </c>
+      <c r="KE49">
+        <v>117034.10897</v>
+      </c>
+      <c r="KF49">
+        <v>430815.83837000001</v>
+      </c>
+      <c r="KG49">
+        <v>76790.166859999998</v>
+      </c>
+      <c r="KH49">
+        <v>53508.284740000003</v>
+      </c>
+      <c r="KI49">
+        <v>67825.668919999996</v>
+      </c>
+      <c r="KJ49">
+        <v>136109.42817</v>
+      </c>
     </row>
-    <row r="50" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>293</v>
       </c>
@@ -40217,8 +42653,56 @@
       <c r="JT50">
         <v>95073.057979999998</v>
       </c>
+      <c r="JU50">
+        <v>190618</v>
+      </c>
+      <c r="JV50">
+        <v>200097.74468999999</v>
+      </c>
+      <c r="JW50">
+        <v>142394.22886</v>
+      </c>
+      <c r="JX50">
+        <v>196704</v>
+      </c>
+      <c r="JY50">
+        <v>189151</v>
+      </c>
+      <c r="JZ50">
+        <v>209600.96556000001</v>
+      </c>
+      <c r="KA50">
+        <v>178176</v>
+      </c>
+      <c r="KB50">
+        <v>189477.81255</v>
+      </c>
+      <c r="KC50">
+        <v>187931</v>
+      </c>
+      <c r="KD50">
+        <v>196553</v>
+      </c>
+      <c r="KE50">
+        <v>330662.36213999998</v>
+      </c>
+      <c r="KF50">
+        <v>162195.75333000001</v>
+      </c>
+      <c r="KG50">
+        <v>87996.210800000001</v>
+      </c>
+      <c r="KH50">
+        <v>165700.17723999999</v>
+      </c>
+      <c r="KI50">
+        <v>133773.88451</v>
+      </c>
+      <c r="KJ50">
+        <v>239252.81211</v>
+      </c>
     </row>
-    <row r="51" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>293</v>
       </c>
@@ -40253,7 +42737,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="52" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>293</v>
       </c>
@@ -40923,8 +43407,56 @@
       <c r="JT52">
         <v>1001242.09705</v>
       </c>
+      <c r="JU52">
+        <v>934104</v>
+      </c>
+      <c r="JV52">
+        <v>1163086.317</v>
+      </c>
+      <c r="JW52">
+        <v>3042709.1731699998</v>
+      </c>
+      <c r="JX52">
+        <v>1084186</v>
+      </c>
+      <c r="JY52">
+        <v>1215304</v>
+      </c>
+      <c r="JZ52">
+        <v>1271288.7239300001</v>
+      </c>
+      <c r="KA52">
+        <v>1044112</v>
+      </c>
+      <c r="KB52">
+        <v>1213374.6196900001</v>
+      </c>
+      <c r="KC52">
+        <v>1161741</v>
+      </c>
+      <c r="KD52">
+        <v>999696</v>
+      </c>
+      <c r="KE52">
+        <v>1285514.2735900001</v>
+      </c>
+      <c r="KF52">
+        <v>922769.80512000003</v>
+      </c>
+      <c r="KG52">
+        <v>937047.16763000004</v>
+      </c>
+      <c r="KH52">
+        <v>1154150.25874</v>
+      </c>
+      <c r="KI52">
+        <v>2764504.9873700002</v>
+      </c>
+      <c r="KJ52">
+        <v>1060028.96468</v>
+      </c>
     </row>
-    <row r="53" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>293</v>
       </c>
@@ -41765,8 +44297,56 @@
       <c r="JT53">
         <v>91880.188399999999</v>
       </c>
+      <c r="JU53">
+        <v>91587</v>
+      </c>
+      <c r="JV53">
+        <v>81996.123770000006</v>
+      </c>
+      <c r="JW53">
+        <v>79968.013019999999</v>
+      </c>
+      <c r="JX53">
+        <v>81016</v>
+      </c>
+      <c r="JY53">
+        <v>96486</v>
+      </c>
+      <c r="JZ53">
+        <v>88006.215379999994</v>
+      </c>
+      <c r="KA53">
+        <v>95515</v>
+      </c>
+      <c r="KB53">
+        <v>96055.86159</v>
+      </c>
+      <c r="KC53">
+        <v>111795</v>
+      </c>
+      <c r="KD53">
+        <v>98858</v>
+      </c>
+      <c r="KE53">
+        <v>84017.006770000007</v>
+      </c>
+      <c r="KF53">
+        <v>100272.75248</v>
+      </c>
+      <c r="KG53">
+        <v>96482.389869999999</v>
+      </c>
+      <c r="KH53">
+        <v>85194.215960000001</v>
+      </c>
+      <c r="KI53">
+        <v>84654.959189999994</v>
+      </c>
+      <c r="KJ53">
+        <v>87512.512239999996</v>
+      </c>
     </row>
-    <row r="54" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>293</v>
       </c>
@@ -42526,8 +45106,56 @@
       <c r="JT54">
         <v>860.63315999999998</v>
       </c>
+      <c r="JU54">
+        <v>899</v>
+      </c>
+      <c r="JV54">
+        <v>163713.26783999999</v>
+      </c>
+      <c r="JW54">
+        <v>1298.45868</v>
+      </c>
+      <c r="JX54">
+        <v>1210</v>
+      </c>
+      <c r="JY54">
+        <v>165487</v>
+      </c>
+      <c r="JZ54">
+        <v>1265.3827200000001</v>
+      </c>
+      <c r="KA54">
+        <v>1375</v>
+      </c>
+      <c r="KB54">
+        <v>197966.24463999999</v>
+      </c>
+      <c r="KC54">
+        <v>812</v>
+      </c>
+      <c r="KD54">
+        <v>1083</v>
+      </c>
+      <c r="KE54">
+        <v>98732.415940000006</v>
+      </c>
+      <c r="KF54">
+        <v>3904.2619</v>
+      </c>
+      <c r="KG54">
+        <v>4438.9376400000001</v>
+      </c>
+      <c r="KH54">
+        <v>158345.61192</v>
+      </c>
+      <c r="KI54">
+        <v>5322.8263200000001</v>
+      </c>
+      <c r="KJ54">
+        <v>951.99645999999996</v>
+      </c>
     </row>
-    <row r="55" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>293</v>
       </c>
@@ -43116,8 +45744,56 @@
       <c r="JT55">
         <v>631808.17081000004</v>
       </c>
+      <c r="JU55">
+        <v>595600</v>
+      </c>
+      <c r="JV55">
+        <v>644387.67076999997</v>
+      </c>
+      <c r="JW55">
+        <v>649915.31096999999</v>
+      </c>
+      <c r="JX55">
+        <v>669440</v>
+      </c>
+      <c r="JY55">
+        <v>645857</v>
+      </c>
+      <c r="JZ55">
+        <v>592835.41428999999</v>
+      </c>
+      <c r="KA55">
+        <v>600877</v>
+      </c>
+      <c r="KB55">
+        <v>566024.86048000003</v>
+      </c>
+      <c r="KC55">
+        <v>516689</v>
+      </c>
+      <c r="KD55">
+        <v>546083</v>
+      </c>
+      <c r="KE55">
+        <v>512020.76224000001</v>
+      </c>
+      <c r="KF55">
+        <v>551328.47540999996</v>
+      </c>
+      <c r="KG55">
+        <v>514167.34386999998</v>
+      </c>
+      <c r="KH55">
+        <v>582073.06600999995</v>
+      </c>
+      <c r="KI55">
+        <v>590887.66275999998</v>
+      </c>
+      <c r="KJ55">
+        <v>613377.34173999995</v>
+      </c>
     </row>
-    <row r="56" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>293</v>
       </c>
@@ -43706,8 +46382,56 @@
       <c r="JT56">
         <v>86.5</v>
       </c>
+      <c r="JU56">
+        <v>537</v>
+      </c>
+      <c r="JV56">
+        <v>766.02</v>
+      </c>
+      <c r="JW56">
+        <v>641.6</v>
+      </c>
+      <c r="JX56">
+        <v>526</v>
+      </c>
+      <c r="JY56">
+        <v>584</v>
+      </c>
+      <c r="JZ56">
+        <v>835</v>
+      </c>
+      <c r="KA56">
+        <v>557</v>
+      </c>
+      <c r="KB56">
+        <v>728.22877000000005</v>
+      </c>
+      <c r="KC56">
+        <v>736</v>
+      </c>
+      <c r="KD56">
+        <v>1032</v>
+      </c>
+      <c r="KE56">
+        <v>1165.8</v>
+      </c>
+      <c r="KF56">
+        <v>92.32</v>
+      </c>
+      <c r="KG56">
+        <v>581.04524000000004</v>
+      </c>
+      <c r="KH56">
+        <v>612.13476000000003</v>
+      </c>
+      <c r="KI56">
+        <v>646.96</v>
+      </c>
+      <c r="KJ56">
+        <v>435.34</v>
+      </c>
     </row>
-    <row r="57" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>293</v>
       </c>
@@ -44260,8 +46984,56 @@
       <c r="JT57">
         <v>200122.27101</v>
       </c>
+      <c r="JU57">
+        <v>201514</v>
+      </c>
+      <c r="JV57">
+        <v>220870.04832999999</v>
+      </c>
+      <c r="JW57">
+        <v>379911.26059999998</v>
+      </c>
+      <c r="JX57">
+        <v>256372</v>
+      </c>
+      <c r="JY57">
+        <v>247123</v>
+      </c>
+      <c r="JZ57">
+        <v>483916.58214999997</v>
+      </c>
+      <c r="KA57">
+        <v>288301</v>
+      </c>
+      <c r="KB57">
+        <v>283088.86038999999</v>
+      </c>
+      <c r="KC57">
+        <v>445783</v>
+      </c>
+      <c r="KD57">
+        <v>288643</v>
+      </c>
+      <c r="KE57">
+        <v>484588.30554999999</v>
+      </c>
+      <c r="KF57">
+        <v>202139.38208000001</v>
+      </c>
+      <c r="KG57">
+        <v>259477.38329</v>
+      </c>
+      <c r="KH57">
+        <v>259174.80833</v>
+      </c>
+      <c r="KI57">
+        <v>479710.8738</v>
+      </c>
+      <c r="KJ57">
+        <v>291411.11725000001</v>
+      </c>
     </row>
-    <row r="58" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>293</v>
       </c>
@@ -44598,8 +47370,56 @@
       <c r="JT58">
         <v>65574.244749999998</v>
       </c>
+      <c r="JU58">
+        <v>43395</v>
+      </c>
+      <c r="JV58">
+        <v>49900.39587</v>
+      </c>
+      <c r="JW58">
+        <v>88451.388279999999</v>
+      </c>
+      <c r="JX58">
+        <v>49370</v>
+      </c>
+      <c r="JY58">
+        <v>44294</v>
+      </c>
+      <c r="JZ58">
+        <v>100250.03195999999</v>
+      </c>
+      <c r="KA58">
+        <v>54239</v>
+      </c>
+      <c r="KB58">
+        <v>66698.240340000004</v>
+      </c>
+      <c r="KC58">
+        <v>83214</v>
+      </c>
+      <c r="KD58">
+        <v>54303</v>
+      </c>
+      <c r="KE58">
+        <v>92489.055550000005</v>
+      </c>
+      <c r="KF58">
+        <v>64656.846519999999</v>
+      </c>
+      <c r="KG58">
+        <v>58270.661070000002</v>
+      </c>
+      <c r="KH58">
+        <v>61250.990640000004</v>
+      </c>
+      <c r="KI58">
+        <v>102780.77615000001</v>
+      </c>
+      <c r="KJ58">
+        <v>48756.991849999999</v>
+      </c>
     </row>
-    <row r="59" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>293</v>
       </c>
@@ -44936,8 +47756,56 @@
       <c r="JT59">
         <v>7282.8113000000003</v>
       </c>
+      <c r="JU59">
+        <v>0</v>
+      </c>
+      <c r="JV59">
+        <v>0</v>
+      </c>
+      <c r="JW59">
+        <v>0</v>
+      </c>
+      <c r="JX59">
+        <v>544</v>
+      </c>
+      <c r="JY59">
+        <v>0</v>
+      </c>
+      <c r="JZ59">
+        <v>0</v>
+      </c>
+      <c r="KA59">
+        <v>0</v>
+      </c>
+      <c r="KB59">
+        <v>0</v>
+      </c>
+      <c r="KC59">
+        <v>0</v>
+      </c>
+      <c r="KD59">
+        <v>0</v>
+      </c>
+      <c r="KE59">
+        <v>0</v>
+      </c>
+      <c r="KF59">
+        <v>0</v>
+      </c>
+      <c r="KG59">
+        <v>0</v>
+      </c>
+      <c r="KH59">
+        <v>0</v>
+      </c>
+      <c r="KI59">
+        <v>2434.6729799999998</v>
+      </c>
+      <c r="KJ59">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>293</v>
       </c>
@@ -45130,8 +47998,56 @@
       <c r="JT60">
         <v>3520.2894900000001</v>
       </c>
+      <c r="JU60">
+        <v>480</v>
+      </c>
+      <c r="JV60">
+        <v>1413.5796499999999</v>
+      </c>
+      <c r="JW60">
+        <v>1842447.9585500001</v>
+      </c>
+      <c r="JX60">
+        <v>21868</v>
+      </c>
+      <c r="JY60">
+        <v>13793</v>
+      </c>
+      <c r="JZ60">
+        <v>4038.8668499999999</v>
+      </c>
+      <c r="KA60">
+        <v>3153</v>
+      </c>
+      <c r="KB60">
+        <v>2140.6123600000001</v>
+      </c>
+      <c r="KC60">
+        <v>2299</v>
+      </c>
+      <c r="KD60">
+        <v>4865</v>
+      </c>
+      <c r="KE60">
+        <v>11825.66201</v>
+      </c>
+      <c r="KF60">
+        <v>200</v>
+      </c>
+      <c r="KG60">
+        <v>3460.4192400000002</v>
+      </c>
+      <c r="KH60">
+        <v>7398.6998599999997</v>
+      </c>
+      <c r="KI60">
+        <v>1498002.2529800001</v>
+      </c>
+      <c r="KJ60">
+        <v>17073.752680000001</v>
+      </c>
     </row>
-    <row r="61" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>293</v>
       </c>
@@ -45145,7 +48061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>293</v>
       </c>
@@ -45189,7 +48105,7 @@
         <v>35076</v>
       </c>
     </row>
-    <row r="63" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>293</v>
       </c>
@@ -45886,8 +48802,56 @@
       <c r="JT63">
         <v>847424.21323999995</v>
       </c>
+      <c r="JU63">
+        <v>613351</v>
+      </c>
+      <c r="JV63">
+        <v>981359.42890000006</v>
+      </c>
+      <c r="JW63">
+        <v>910193.64939999999</v>
+      </c>
+      <c r="JX63">
+        <v>781674</v>
+      </c>
+      <c r="JY63">
+        <v>818464</v>
+      </c>
+      <c r="JZ63">
+        <v>1035521.3419</v>
+      </c>
+      <c r="KA63">
+        <v>374698</v>
+      </c>
+      <c r="KB63">
+        <v>898124.49178000004</v>
+      </c>
+      <c r="KC63">
+        <v>593047</v>
+      </c>
+      <c r="KD63">
+        <v>711368</v>
+      </c>
+      <c r="KE63">
+        <v>1513949.3324599999</v>
+      </c>
+      <c r="KF63">
+        <v>1024597.43351</v>
+      </c>
+      <c r="KG63">
+        <v>578175.49069999997</v>
+      </c>
+      <c r="KH63">
+        <v>1415410.4506999999</v>
+      </c>
+      <c r="KI63">
+        <v>1686706.90114</v>
+      </c>
+      <c r="KJ63">
+        <v>1061915.0591800001</v>
+      </c>
     </row>
-    <row r="64" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>293</v>
       </c>
@@ -46590,8 +49554,56 @@
       <c r="JT64">
         <v>57.228189999999998</v>
       </c>
+      <c r="JU64">
+        <v>4095</v>
+      </c>
+      <c r="JV64">
+        <v>118.92977</v>
+      </c>
+      <c r="JW64">
+        <v>611.65074000000004</v>
+      </c>
+      <c r="JX64">
+        <v>62471</v>
+      </c>
+      <c r="JY64">
+        <v>5873</v>
+      </c>
+      <c r="JZ64">
+        <v>31097.026620000001</v>
+      </c>
+      <c r="KA64">
+        <v>0</v>
+      </c>
+      <c r="KB64">
+        <v>163034.38227999999</v>
+      </c>
+      <c r="KC64">
+        <v>2074</v>
+      </c>
+      <c r="KD64">
+        <v>1116</v>
+      </c>
+      <c r="KE64">
+        <v>4993.7478000000001</v>
+      </c>
+      <c r="KF64">
+        <v>0</v>
+      </c>
+      <c r="KG64">
+        <v>10518.32105</v>
+      </c>
+      <c r="KH64">
+        <v>256.85324000000003</v>
+      </c>
+      <c r="KI64">
+        <v>1008.7472299999999</v>
+      </c>
+      <c r="KJ64">
+        <v>5205.8478299999997</v>
+      </c>
     </row>
-    <row r="65" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>229</v>
       </c>
@@ -47432,8 +50444,56 @@
       <c r="JT65">
         <v>3346580.4558700002</v>
       </c>
+      <c r="JU65">
+        <v>5983119</v>
+      </c>
+      <c r="JV65">
+        <v>6578886.1801100001</v>
+      </c>
+      <c r="JW65">
+        <v>7058148.0851699999</v>
+      </c>
+      <c r="JX65">
+        <v>6518645</v>
+      </c>
+      <c r="JY65">
+        <v>7032176</v>
+      </c>
+      <c r="JZ65">
+        <v>8669931.0858699996</v>
+      </c>
+      <c r="KA65">
+        <v>6990088</v>
+      </c>
+      <c r="KB65">
+        <v>7017016.2540899999</v>
+      </c>
+      <c r="KC65">
+        <v>6304345</v>
+      </c>
+      <c r="KD65">
+        <v>6748019</v>
+      </c>
+      <c r="KE65">
+        <v>12013033.54998</v>
+      </c>
+      <c r="KF65">
+        <v>2601718.9531100001</v>
+      </c>
+      <c r="KG65">
+        <v>6687125.2461999999</v>
+      </c>
+      <c r="KH65">
+        <v>6868001.87127</v>
+      </c>
+      <c r="KI65">
+        <v>8168218.8056899998</v>
+      </c>
+      <c r="KJ65">
+        <v>7241288.1269399999</v>
+      </c>
     </row>
-    <row r="66" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>229</v>
       </c>
@@ -48130,8 +51190,56 @@
       <c r="JT66">
         <v>2969841.5620599999</v>
       </c>
+      <c r="JU66">
+        <v>5778521</v>
+      </c>
+      <c r="JV66">
+        <v>6140832.0484199999</v>
+      </c>
+      <c r="JW66">
+        <v>6785537.0219400004</v>
+      </c>
+      <c r="JX66">
+        <v>6361241</v>
+      </c>
+      <c r="JY66">
+        <v>6780828</v>
+      </c>
+      <c r="JZ66">
+        <v>8274643.5269799996</v>
+      </c>
+      <c r="KA66">
+        <v>7011766</v>
+      </c>
+      <c r="KB66">
+        <v>6858658.7722800002</v>
+      </c>
+      <c r="KC66">
+        <v>6296595</v>
+      </c>
+      <c r="KD66">
+        <v>6734743</v>
+      </c>
+      <c r="KE66">
+        <v>11542172.348719999</v>
+      </c>
+      <c r="KF66">
+        <v>2196562.7146600001</v>
+      </c>
+      <c r="KG66">
+        <v>6739388.8278400004</v>
+      </c>
+      <c r="KH66">
+        <v>6731381.8986900002</v>
+      </c>
+      <c r="KI66">
+        <v>8045825.3140099999</v>
+      </c>
+      <c r="KJ66">
+        <v>7174427.3579700002</v>
+      </c>
     </row>
-    <row r="67" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>229</v>
       </c>
@@ -48972,8 +52080,56 @@
       <c r="JT67">
         <v>2860229.9446899998</v>
       </c>
+      <c r="JU67">
+        <v>5212048</v>
+      </c>
+      <c r="JV67">
+        <v>5391581.1671000002</v>
+      </c>
+      <c r="JW67">
+        <v>6110298.1308899997</v>
+      </c>
+      <c r="JX67">
+        <v>5572803</v>
+      </c>
+      <c r="JY67">
+        <v>5949543</v>
+      </c>
+      <c r="JZ67">
+        <v>7194836.0959799998</v>
+      </c>
+      <c r="KA67">
+        <v>5973401</v>
+      </c>
+      <c r="KB67">
+        <v>5850706.0432900004</v>
+      </c>
+      <c r="KC67">
+        <v>5687540</v>
+      </c>
+      <c r="KD67">
+        <v>5926388</v>
+      </c>
+      <c r="KE67">
+        <v>10261619.31951</v>
+      </c>
+      <c r="KF67">
+        <v>2081855.6004900001</v>
+      </c>
+      <c r="KG67">
+        <v>5981539.9084400004</v>
+      </c>
+      <c r="KH67">
+        <v>6062415.0789700001</v>
+      </c>
+      <c r="KI67">
+        <v>7332306.0565099996</v>
+      </c>
+      <c r="KJ67">
+        <v>6364498.2436499996</v>
+      </c>
     </row>
-    <row r="68" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>229</v>
       </c>
@@ -49020,7 +52176,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="69" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>229</v>
       </c>
@@ -49055,7 +52211,7 @@
         <v>-655</v>
       </c>
     </row>
-    <row r="70" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>229</v>
       </c>
@@ -49536,8 +52692,56 @@
       <c r="JT70">
         <v>109611.61737000001</v>
       </c>
+      <c r="JU70">
+        <v>566473</v>
+      </c>
+      <c r="JV70">
+        <v>749250.88132000004</v>
+      </c>
+      <c r="JW70">
+        <v>675238.89104999998</v>
+      </c>
+      <c r="JX70">
+        <v>788438</v>
+      </c>
+      <c r="JY70">
+        <v>831285</v>
+      </c>
+      <c r="JZ70">
+        <v>1079807.4310000001</v>
+      </c>
+      <c r="KA70">
+        <v>1038365</v>
+      </c>
+      <c r="KB70">
+        <v>1007952.72899</v>
+      </c>
+      <c r="KC70">
+        <v>609055</v>
+      </c>
+      <c r="KD70">
+        <v>808355</v>
+      </c>
+      <c r="KE70">
+        <v>1280553.0292100001</v>
+      </c>
+      <c r="KF70">
+        <v>114707.11417</v>
+      </c>
+      <c r="KG70">
+        <v>757848.91940000001</v>
+      </c>
+      <c r="KH70">
+        <v>668966.81972000003</v>
+      </c>
+      <c r="KI70">
+        <v>713519.25749999995</v>
+      </c>
+      <c r="KJ70">
+        <v>809929.11432000005</v>
+      </c>
     </row>
-    <row r="71" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>229</v>
       </c>
@@ -49802,8 +53006,56 @@
       <c r="JT71">
         <v>788.39953000000003</v>
       </c>
+      <c r="JU71">
+        <v>14452</v>
+      </c>
+      <c r="JV71">
+        <v>10086.80011</v>
+      </c>
+      <c r="JW71">
+        <v>12548.126840000001</v>
+      </c>
+      <c r="JX71">
+        <v>15422</v>
+      </c>
+      <c r="JY71">
+        <v>17129</v>
+      </c>
+      <c r="JZ71">
+        <v>15246.103069999999</v>
+      </c>
+      <c r="KA71">
+        <v>12809</v>
+      </c>
+      <c r="KB71">
+        <v>14255.24073</v>
+      </c>
+      <c r="KC71">
+        <v>15047</v>
+      </c>
+      <c r="KD71">
+        <v>9472</v>
+      </c>
+      <c r="KE71">
+        <v>25570.315790000001</v>
+      </c>
+      <c r="KF71">
+        <v>3425.1573899999999</v>
+      </c>
+      <c r="KG71">
+        <v>19558.526669999999</v>
+      </c>
+      <c r="KH71">
+        <v>17458.42628</v>
+      </c>
+      <c r="KI71">
+        <v>21065.56941</v>
+      </c>
+      <c r="KJ71">
+        <v>11917.555039999999</v>
+      </c>
     </row>
-    <row r="72" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>229</v>
       </c>
@@ -50500,8 +53752,56 @@
       <c r="JT72">
         <v>847424.21323999995</v>
       </c>
+      <c r="JU72">
+        <v>613351</v>
+      </c>
+      <c r="JV72">
+        <v>981359.42890000006</v>
+      </c>
+      <c r="JW72">
+        <v>910193.64939999999</v>
+      </c>
+      <c r="JX72">
+        <v>781674</v>
+      </c>
+      <c r="JY72">
+        <v>818464</v>
+      </c>
+      <c r="JZ72">
+        <v>1035521.3419</v>
+      </c>
+      <c r="KA72">
+        <v>374698</v>
+      </c>
+      <c r="KB72">
+        <v>898124.49178000004</v>
+      </c>
+      <c r="KC72">
+        <v>593047</v>
+      </c>
+      <c r="KD72">
+        <v>711368</v>
+      </c>
+      <c r="KE72">
+        <v>1513949.3324599999</v>
+      </c>
+      <c r="KF72">
+        <v>1024597.43351</v>
+      </c>
+      <c r="KG72">
+        <v>578175.49069999997</v>
+      </c>
+      <c r="KH72">
+        <v>1415410.4506999999</v>
+      </c>
+      <c r="KI72">
+        <v>1686706.90114</v>
+      </c>
+      <c r="KJ72">
+        <v>1061915.0591800001</v>
+      </c>
     </row>
-    <row r="73" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>229</v>
       </c>
@@ -51342,8 +54642,56 @@
       <c r="JT73">
         <v>344024.92327000003</v>
       </c>
+      <c r="JU73">
+        <v>157993</v>
+      </c>
+      <c r="JV73">
+        <v>400510.50043999997</v>
+      </c>
+      <c r="JW73">
+        <v>232909.90491000001</v>
+      </c>
+      <c r="JX73">
+        <v>111968</v>
+      </c>
+      <c r="JY73">
+        <v>182470</v>
+      </c>
+      <c r="JZ73">
+        <v>348470.09259999997</v>
+      </c>
+      <c r="KA73">
+        <v>-57790</v>
+      </c>
+      <c r="KB73">
+        <v>124204.80223</v>
+      </c>
+      <c r="KC73">
+        <v>-32986</v>
+      </c>
+      <c r="KD73">
+        <v>-21090</v>
+      </c>
+      <c r="KE73">
+        <v>397436.26656999998</v>
+      </c>
+      <c r="KF73">
+        <v>368926.75575999997</v>
+      </c>
+      <c r="KG73">
+        <v>-94687.301300000006</v>
+      </c>
+      <c r="KH73">
+        <v>99880.718150000001</v>
+      </c>
+      <c r="KI73">
+        <v>76539.004239999995</v>
+      </c>
+      <c r="KJ73">
+        <v>38235.837579999999</v>
+      </c>
     </row>
-    <row r="74" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>229</v>
       </c>
@@ -52055,8 +55403,56 @@
       <c r="JT74">
         <v>1433.50126</v>
       </c>
+      <c r="JU74">
+        <v>202</v>
+      </c>
+      <c r="JV74">
+        <v>106.61494999999999</v>
+      </c>
+      <c r="JW74">
+        <v>2595.9322299999999</v>
+      </c>
+      <c r="JX74">
+        <v>6736</v>
+      </c>
+      <c r="JY74">
+        <v>22649</v>
+      </c>
+      <c r="JZ74">
+        <v>1090.8720499999999</v>
+      </c>
+      <c r="KA74">
+        <v>162</v>
+      </c>
+      <c r="KB74">
+        <v>0</v>
+      </c>
+      <c r="KC74">
+        <v>10542</v>
+      </c>
+      <c r="KD74">
+        <v>1847</v>
+      </c>
+      <c r="KE74">
+        <v>16044.954229999999</v>
+      </c>
+      <c r="KF74">
+        <v>2878.4159</v>
+      </c>
+      <c r="KG74">
+        <v>700.05499999999995</v>
+      </c>
+      <c r="KH74">
+        <v>2115</v>
+      </c>
+      <c r="KI74">
+        <v>4095.1969600000002</v>
+      </c>
+      <c r="KJ74">
+        <v>3424.3599399999998</v>
+      </c>
     </row>
-    <row r="75" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>229</v>
       </c>
@@ -52213,8 +55609,56 @@
       <c r="JT75">
         <v>30492.069749999999</v>
       </c>
+      <c r="JU75">
+        <v>31951</v>
+      </c>
+      <c r="JV75">
+        <v>27350.216189999999</v>
+      </c>
+      <c r="JW75">
+        <v>24557.099249999999</v>
+      </c>
+      <c r="JX75">
+        <v>23278</v>
+      </c>
+      <c r="JY75">
+        <v>29100</v>
+      </c>
+      <c r="JZ75">
+        <v>30480.491170000001</v>
+      </c>
+      <c r="KA75">
+        <v>23141</v>
+      </c>
+      <c r="KB75">
+        <v>19897.438849999999</v>
+      </c>
+      <c r="KC75">
+        <v>15147</v>
+      </c>
+      <c r="KD75">
+        <v>23047</v>
+      </c>
+      <c r="KE75">
+        <v>31809.664669999998</v>
+      </c>
+      <c r="KF75">
+        <v>29925.9094</v>
+      </c>
+      <c r="KG75">
+        <v>22165.137989999999</v>
+      </c>
+      <c r="KH75">
+        <v>17165.828150000001</v>
+      </c>
+      <c r="KI75">
+        <v>20693.72107</v>
+      </c>
+      <c r="KJ75">
+        <v>13283.01641</v>
+      </c>
     </row>
-    <row r="76" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>236</v>
       </c>
@@ -53055,8 +56499,56 @@
       <c r="JT76">
         <v>0</v>
       </c>
+      <c r="JU76">
+        <v>0</v>
+      </c>
+      <c r="JV76">
+        <v>0</v>
+      </c>
+      <c r="JW76">
+        <v>0</v>
+      </c>
+      <c r="JX76">
+        <v>1</v>
+      </c>
+      <c r="JY76">
+        <v>-1</v>
+      </c>
+      <c r="JZ76">
+        <v>0</v>
+      </c>
+      <c r="KA76">
+        <v>0</v>
+      </c>
+      <c r="KB76">
+        <v>0</v>
+      </c>
+      <c r="KC76">
+        <v>0</v>
+      </c>
+      <c r="KD76">
+        <v>0</v>
+      </c>
+      <c r="KE76">
+        <v>0</v>
+      </c>
+      <c r="KF76">
+        <v>0</v>
+      </c>
+      <c r="KG76">
+        <v>0</v>
+      </c>
+      <c r="KH76">
+        <v>0</v>
+      </c>
+      <c r="KI76">
+        <v>0</v>
+      </c>
+      <c r="KJ76">
+        <v>0</v>
+      </c>
     </row>
-    <row r="77" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>236</v>
       </c>
@@ -53897,8 +57389,56 @@
       <c r="JT77">
         <v>0</v>
       </c>
+      <c r="JU77">
+        <v>0</v>
+      </c>
+      <c r="JV77">
+        <v>0</v>
+      </c>
+      <c r="JW77">
+        <v>0</v>
+      </c>
+      <c r="JX77">
+        <v>1</v>
+      </c>
+      <c r="JY77">
+        <v>-1</v>
+      </c>
+      <c r="JZ77">
+        <v>0</v>
+      </c>
+      <c r="KA77">
+        <v>0</v>
+      </c>
+      <c r="KB77">
+        <v>0</v>
+      </c>
+      <c r="KC77">
+        <v>0</v>
+      </c>
+      <c r="KD77">
+        <v>0</v>
+      </c>
+      <c r="KE77">
+        <v>0</v>
+      </c>
+      <c r="KF77">
+        <v>0</v>
+      </c>
+      <c r="KG77">
+        <v>0</v>
+      </c>
+      <c r="KH77">
+        <v>0</v>
+      </c>
+      <c r="KI77">
+        <v>0</v>
+      </c>
+      <c r="KJ77">
+        <v>0</v>
+      </c>
     </row>
-    <row r="78" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>238</v>
       </c>
@@ -54703,8 +58243,56 @@
       <c r="JT78">
         <v>-453.20654000000002</v>
       </c>
+      <c r="JU78">
+        <v>-684</v>
+      </c>
+      <c r="JV78">
+        <v>-534.82234000000005</v>
+      </c>
+      <c r="JW78">
+        <v>-3834.58329</v>
+      </c>
+      <c r="JX78">
+        <v>-791</v>
+      </c>
+      <c r="JY78">
+        <v>-1113</v>
+      </c>
+      <c r="JZ78">
+        <v>-19324.07357</v>
+      </c>
+      <c r="KA78">
+        <v>-13133</v>
+      </c>
+      <c r="KB78">
+        <v>-3232.1685400000001</v>
+      </c>
+      <c r="KC78">
+        <v>-479</v>
+      </c>
+      <c r="KD78">
+        <v>-1498</v>
+      </c>
+      <c r="KE78">
+        <v>-5768.99791</v>
+      </c>
+      <c r="KF78">
+        <v>94.864320000000006</v>
+      </c>
+      <c r="KG78">
+        <v>-1136.81675</v>
+      </c>
+      <c r="KH78">
+        <v>-2463.8681999999999</v>
+      </c>
+      <c r="KI78">
+        <v>-646.85657000000003</v>
+      </c>
+      <c r="KJ78">
+        <v>-830.31965000000002</v>
+      </c>
     </row>
-    <row r="79" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>239</v>
       </c>
@@ -55545,8 +59133,56 @@
       <c r="JT79">
         <v>121335125.05666</v>
       </c>
+      <c r="JU79">
+        <v>134496181</v>
+      </c>
+      <c r="JV79">
+        <v>206797753.87049001</v>
+      </c>
+      <c r="JW79">
+        <v>120967798.37164</v>
+      </c>
+      <c r="JX79">
+        <v>175983728</v>
+      </c>
+      <c r="JY79">
+        <v>165144219</v>
+      </c>
+      <c r="JZ79">
+        <v>137082749.39302999</v>
+      </c>
+      <c r="KA79">
+        <v>141038632</v>
+      </c>
+      <c r="KB79">
+        <v>227678817.05452999</v>
+      </c>
+      <c r="KC79">
+        <v>155525880</v>
+      </c>
+      <c r="KD79">
+        <v>214829619</v>
+      </c>
+      <c r="KE79">
+        <v>209459901.55956</v>
+      </c>
+      <c r="KF79">
+        <v>133559283.10037</v>
+      </c>
+      <c r="KG79">
+        <v>142980302.83305001</v>
+      </c>
+      <c r="KH79">
+        <v>228823559.26835001</v>
+      </c>
+      <c r="KI79">
+        <v>120821266.95213</v>
+      </c>
+      <c r="KJ79">
+        <v>193593841.23249</v>
+      </c>
     </row>
-    <row r="80" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>240</v>
       </c>
@@ -56294,8 +59930,56 @@
       <c r="JT80">
         <v>-18388029</v>
       </c>
+      <c r="JU80">
+        <v>0</v>
+      </c>
+      <c r="JV80">
+        <v>0</v>
+      </c>
+      <c r="JW80">
+        <v>-18388029</v>
+      </c>
+      <c r="JX80">
+        <v>0</v>
+      </c>
+      <c r="JY80">
+        <v>0</v>
+      </c>
+      <c r="JZ80">
+        <v>-18388029</v>
+      </c>
+      <c r="KA80">
+        <v>0</v>
+      </c>
+      <c r="KB80">
+        <v>0</v>
+      </c>
+      <c r="KC80">
+        <v>-18388028</v>
+      </c>
+      <c r="KD80">
+        <v>0</v>
+      </c>
+      <c r="KE80">
+        <v>0</v>
+      </c>
+      <c r="KF80">
+        <v>-19601924</v>
+      </c>
+      <c r="KG80">
+        <v>0</v>
+      </c>
+      <c r="KH80">
+        <v>0</v>
+      </c>
+      <c r="KI80">
+        <v>-19601924</v>
+      </c>
+      <c r="KJ80">
+        <v>0</v>
+      </c>
     </row>
-    <row r="81" spans="1:280" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:296" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>241</v>
       </c>
@@ -57135,6 +60819,54 @@
       </c>
       <c r="JT81">
         <v>102947096.05666</v>
+      </c>
+      <c r="JU81">
+        <v>134496181</v>
+      </c>
+      <c r="JV81">
+        <v>206797753.87049001</v>
+      </c>
+      <c r="JW81">
+        <v>102579769.37164</v>
+      </c>
+      <c r="JX81">
+        <v>175983728</v>
+      </c>
+      <c r="JY81">
+        <v>165144219</v>
+      </c>
+      <c r="JZ81">
+        <v>118694720.39303</v>
+      </c>
+      <c r="KA81">
+        <v>141038632</v>
+      </c>
+      <c r="KB81">
+        <v>227678817.05452999</v>
+      </c>
+      <c r="KC81">
+        <v>137137852</v>
+      </c>
+      <c r="KD81">
+        <v>214829619</v>
+      </c>
+      <c r="KE81">
+        <v>209459901.55956</v>
+      </c>
+      <c r="KF81">
+        <v>113957359.10037</v>
+      </c>
+      <c r="KG81">
+        <v>142980302.83305001</v>
+      </c>
+      <c r="KH81">
+        <v>228823559.26835001</v>
+      </c>
+      <c r="KI81">
+        <v>101219342.95213</v>
+      </c>
+      <c r="KJ81">
+        <v>193593841.23249</v>
       </c>
     </row>
   </sheetData>
